--- a/연구코드/results/feature_selection/gangnam/feature_selection_summary.xlsx
+++ b/연구코드/results/feature_selection/gangnam/feature_selection_summary.xlsx
@@ -47,7 +47,7 @@
     <t>VIF pruning (VIF&gt;10)</t>
   </si>
   <si>
-    <t>band4_energy, p25, fft_mag_std, band2_energy_ratio, band1_energy, median, p75, wavelet_cA_energy, band4_energy_ratio, p95, wavelet_cA_std, band3_energy_ratio, p90, AUC_normalized, peak_mean_height, AUC, mean_abs_deviation, spectral_rolloff, band3_energy, RMSE</t>
+    <t>fft_mag_std, wavelet_cA_std, p90, band3_energy, band2_energy_ratio, p95, band1_energy, RMSE, p75, band4_energy, peak_mean_height, AUC, p25, AUC_normalized, band3_energy_ratio, median, band4_energy_ratio, wavelet_cA_energy, mean_abs_deviation, spectral_rolloff</t>
   </si>
   <si>
     <t>CV, IQR, band1_energy_ratio, band2_energy, dominant_freq, min, p10, p5, p90_p10_ratio, signal_energy, signal_length, slope_abs_mean, slope_max, slope_mean, slope_std, spectral_energy, spectral_spread, wavelet_cD1_energy, wavelet_cD1_std, wavelet_cD2_energy, wavelet_cD2_std, wavelet_energy_ratio_D1</t>
@@ -71,27 +71,27 @@
     <t>exhaustive_or_SFS_best</t>
   </si>
   <si>
+    <t>RFE_only</t>
+  </si>
+  <si>
     <t>vote_ge3</t>
   </si>
   <si>
-    <t>RFE_only</t>
-  </si>
-  <si>
     <t>LASSO_only</t>
   </si>
   <si>
+    <t>vote_ge2</t>
+  </si>
+  <si>
     <t>vote_ge1</t>
   </si>
   <si>
+    <t>union_all</t>
+  </si>
+  <si>
     <t>RF_Perm_only</t>
   </si>
   <si>
-    <t>vote_ge2</t>
-  </si>
-  <si>
-    <t>union_all</t>
-  </si>
-  <si>
     <t>CV, IQR, band1_energy_ratio, band2_energy, dominant_freq, max, mean, min, p10, p5, p90_p10_ratio, signal_energy, signal_length, slope_abs_mean, slope_max, slope_mean, slope_min, slope_std, spectral_energy, spectral_spread, std, wavelet_cD1_energy, wavelet_cD1_std, wavelet_cD2_energy, wavelet_cD2_std</t>
   </si>
   <si>
@@ -122,133 +122,133 @@
     <t>p_value</t>
   </si>
   <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>slope_std</t>
+  </si>
+  <si>
+    <t>spectral_energy</t>
+  </si>
+  <si>
+    <t>wavelet_cD2_energy</t>
+  </si>
+  <si>
+    <t>slope_abs_mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>p10</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>dominant_freq</t>
+  </si>
+  <si>
+    <t>slope_mean</t>
+  </si>
+  <si>
     <t>max</t>
   </si>
   <si>
+    <t>IQR</t>
+  </si>
+  <si>
+    <t>wavelet_cD1_std</t>
+  </si>
+  <si>
+    <t>slope_min</t>
+  </si>
+  <si>
+    <t>p90_p10_ratio</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>band2_energy</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
+    <t>band1_energy_ratio</t>
+  </si>
+  <si>
+    <t>wavelet_cD1_energy</t>
+  </si>
+  <si>
+    <t>signal_length</t>
+  </si>
+  <si>
     <t>signal_energy</t>
   </si>
   <si>
-    <t>wavelet_cD1_std</t>
-  </si>
-  <si>
-    <t>p90_p10_ratio</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>dominant_freq</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>signal_length</t>
-  </si>
-  <si>
-    <t>spectral_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD1_energy</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>slope_abs_mean</t>
-  </si>
-  <si>
-    <t>IQR</t>
+    <t>wavelet_cD2_std</t>
   </si>
   <si>
     <t>slope_max</t>
   </si>
   <si>
-    <t>slope_mean</t>
-  </si>
-  <si>
-    <t>band2_energy</t>
-  </si>
-  <si>
-    <t>p10</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_std</t>
-  </si>
-  <si>
-    <t>band1_energy_ratio</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>slope_std</t>
-  </si>
-  <si>
-    <t>p5</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_energy</t>
+    <t>peak_count</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>peak_max_height</t>
+  </si>
+  <si>
+    <t>wavelet_energy_ratio_D1</t>
+  </si>
+  <si>
+    <t>peak_main_pos</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_energy</t>
+  </si>
+  <si>
+    <t>peak_max_width</t>
+  </si>
+  <si>
+    <t>skewness</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
   </si>
   <si>
     <t>first_high_pos</t>
   </si>
   <si>
+    <t>peak_first_pos</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
+    <t>peak_std_height</t>
+  </si>
+  <si>
+    <t>peak_last_pos</t>
+  </si>
+  <si>
+    <t>zero_crossing_rate</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
+    <t>fft_mag_max</t>
+  </si>
+  <si>
     <t>valley_count</t>
-  </si>
-  <si>
-    <t>peak_count</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_energy</t>
-  </si>
-  <si>
-    <t>peak_std_height</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
-    <t>peak_mean_width</t>
-  </si>
-  <si>
-    <t>skewness</t>
-  </si>
-  <si>
-    <t>fft_mag_max</t>
-  </si>
-  <si>
-    <t>wavelet_energy_ratio_D1</t>
-  </si>
-  <si>
-    <t>peak_last_pos</t>
-  </si>
-  <si>
-    <t>peak_first_pos</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>zero_crossing_rate</t>
-  </si>
-  <si>
-    <t>kurtosis</t>
-  </si>
-  <si>
-    <t>peak_max_height</t>
-  </si>
-  <si>
-    <t>peak_max_width</t>
   </si>
   <si>
     <t>range</t>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>0.3062584100234443</v>
+        <v>0.3062584100234444</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -733,7 +733,7 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>0.3042395298783715</v>
+        <v>0.3042395298783716</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -747,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>0.3042395298783713</v>
+        <v>0.3042395298783716</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -803,7 +803,7 @@
         <v>43</v>
       </c>
       <c r="C8">
-        <v>0.2829985661317456</v>
+        <v>0.2829985661317455</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -876,13 +876,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.06352246185843669</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.2110596997711981</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="H2">
-        <v>2.604705109483967E-18</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,13 +902,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.09373792849992224</v>
+        <v>0.0406112356812498</v>
       </c>
       <c r="G3">
-        <v>0.3239516425453906</v>
+        <v>0.1577073432284136</v>
       </c>
       <c r="H3">
-        <v>3.342683028581172E-42</v>
+        <v>8.678327498074129E-11</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0.02610368711778488</v>
+        <v>0.01726766539656444</v>
       </c>
       <c r="G4">
-        <v>0.04347310173721555</v>
+        <v>-0.07391748849713509</v>
       </c>
       <c r="H4">
-        <v>0.07537196198872829</v>
+        <v>0.002476633652844342</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -954,13 +954,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.04944890453170903</v>
+        <v>0.03039388235694229</v>
       </c>
       <c r="G5">
-        <v>-0.3516233652116398</v>
+        <v>0.1008436343579578</v>
       </c>
       <c r="H5">
-        <v>6.689389489174903E-50</v>
+        <v>3.573892182348782E-05</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.01662128920228589</v>
+        <v>0.03083395646531173</v>
       </c>
       <c r="G6">
-        <v>-0.1433422766507355</v>
+        <v>0.07771813486143136</v>
       </c>
       <c r="H6">
-        <v>3.842190132128082E-09</v>
+        <v>0.001461402009404134</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1006,13 +1006,13 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.1244117085663152</v>
+        <v>0.01662128920228589</v>
       </c>
       <c r="G7">
-        <v>0.1919972091980031</v>
+        <v>-0.1433422766507355</v>
       </c>
       <c r="H7">
-        <v>2.310364951717366E-15</v>
+        <v>3.842190132128082E-09</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1032,13 +1032,13 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.09596665305041707</v>
       </c>
       <c r="G8">
-        <v>0.07275059108621751</v>
+        <v>-0.3596962663427493</v>
       </c>
       <c r="H8">
-        <v>0.00289870113315105</v>
+        <v>2.683797095732755E-52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0.07250003352390966</v>
+        <v>0.06771094929525123</v>
       </c>
       <c r="G9">
-        <v>0.2510824608572515</v>
+        <v>0.3527055263853811</v>
       </c>
       <c r="H9">
-        <v>1.756039598366772E-25</v>
+        <v>3.222212217089366E-50</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1084,13 +1084,13 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.01726766539656444</v>
+        <v>0.03469304690640485</v>
       </c>
       <c r="G10">
-        <v>-0.07391748849713509</v>
+        <v>0.2990449750900401</v>
       </c>
       <c r="H10">
-        <v>0.002476633652844342</v>
+        <v>6.290811487188656E-36</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1110,13 +1110,13 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.0657404120324192</v>
+        <v>0.1244117085663152</v>
       </c>
       <c r="G11">
-        <v>0.07682973054579313</v>
+        <v>0.1919972091980031</v>
       </c>
       <c r="H11">
-        <v>0.00165658229630614</v>
+        <v>2.310364951717366E-15</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1136,13 +1136,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.09596665305041707</v>
+        <v>0.00322926317430916</v>
       </c>
       <c r="G12">
-        <v>-0.3596962663427493</v>
+        <v>0.1081780747048873</v>
       </c>
       <c r="H12">
-        <v>2.683797095732755E-52</v>
+        <v>9.174239567674161E-06</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0.03083395646531173</v>
+        <v>0.06352246185843669</v>
       </c>
       <c r="G13">
-        <v>0.07771813486143136</v>
+        <v>0.2110596997711981</v>
       </c>
       <c r="H13">
-        <v>0.001461402009404134</v>
+        <v>2.604705109483967E-18</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1214,13 +1214,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0.01785398632339419</v>
+        <v>0.02610368711778488</v>
       </c>
       <c r="G15">
-        <v>0.07486418638892788</v>
+        <v>0.04347310173721555</v>
       </c>
       <c r="H15">
-        <v>0.002176350543611736</v>
+        <v>0.07537196198872829</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1240,13 +1240,13 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0.00322926317430916</v>
+        <v>0.06789273411413177</v>
       </c>
       <c r="G16">
-        <v>0.1081780747048873</v>
+        <v>-0.1225321729843732</v>
       </c>
       <c r="H16">
-        <v>9.174239567674161E-06</v>
+        <v>4.941706043205827E-07</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1266,13 +1266,13 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0.003864716707023597</v>
+        <v>0.04944890453170903</v>
       </c>
       <c r="G17">
-        <v>-0.01719139192159592</v>
+        <v>-0.3516233652116398</v>
       </c>
       <c r="H17">
-        <v>0.4821152548824258</v>
+        <v>6.689389489174903E-50</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1292,13 +1292,13 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0.06771094929525123</v>
+        <v>0.06730688815940855</v>
       </c>
       <c r="G18">
-        <v>0.3527055263853811</v>
+        <v>0.3064271188370573</v>
       </c>
       <c r="H18">
-        <v>3.222212217089366E-50</v>
+        <v>1.003867397414242E-37</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1318,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0.05203154196427651</v>
+        <v>0.003864716707023597</v>
       </c>
       <c r="G19">
-        <v>0.06941533395191302</v>
+        <v>-0.01719139192159592</v>
       </c>
       <c r="H19">
-        <v>0.004491549210741101</v>
+        <v>0.4821152548824258</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0.008979878659193474</v>
+        <v>0.03961424326443108</v>
       </c>
       <c r="G20">
-        <v>-0.08778557438798017</v>
+        <v>0.2942299536207652</v>
       </c>
       <c r="H20">
-        <v>0.0003231877396473665</v>
+        <v>8.767952186342553E-35</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1370,13 +1370,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0.03469304690640485</v>
+        <v>0.008979878659193474</v>
       </c>
       <c r="G21">
-        <v>0.2990449750900401</v>
+        <v>-0.08778557438798017</v>
       </c>
       <c r="H21">
-        <v>6.290811487188656E-36</v>
+        <v>0.0003231877396473665</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1396,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.06789273411413177</v>
+        <v>0.0657404120324192</v>
       </c>
       <c r="G22">
-        <v>-0.1225321729843732</v>
+        <v>0.07682973054579313</v>
       </c>
       <c r="H22">
-        <v>4.941706043205827E-07</v>
+        <v>0.00165658229630614</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1422,13 +1422,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0.0406112356812498</v>
+        <v>0.07250003352390966</v>
       </c>
       <c r="G23">
-        <v>0.1577073432284136</v>
+        <v>0.2510824608572515</v>
       </c>
       <c r="H23">
-        <v>8.678327498074129E-11</v>
+        <v>1.756039598366772E-25</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1448,13 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0.03961424326443108</v>
+        <v>0.09373792849992224</v>
       </c>
       <c r="G24">
-        <v>0.2942299536207652</v>
+        <v>0.3239516425453906</v>
       </c>
       <c r="H24">
-        <v>8.767952186342553E-35</v>
+        <v>3.342683028581172E-42</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1474,13 +1474,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0.06730688815940855</v>
+        <v>0.05203154196427651</v>
       </c>
       <c r="G25">
-        <v>0.3064271188370573</v>
+        <v>0.06941533395191302</v>
       </c>
       <c r="H25">
-        <v>1.003867397414242E-37</v>
+        <v>0.004491549210741101</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1500,13 +1500,13 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0.03039388235694229</v>
+        <v>0.01785398632339419</v>
       </c>
       <c r="G26">
-        <v>0.1008436343579578</v>
+        <v>0.07486418638892788</v>
       </c>
       <c r="H26">
-        <v>3.573892182348782E-05</v>
+        <v>0.002176350543611736</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>0.03798550812554335</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>0.07785472898280013</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="H27">
-        <v>0.001433344199615437</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1552,13 +1552,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0.01005952120541931</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0.135979414860015</v>
+        <v>0.2482953503862996</v>
       </c>
       <c r="H28">
-        <v>2.332423270366468E-08</v>
+        <v>6.140762423516477E-25</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.0665259280122994</v>
       </c>
       <c r="G29">
-        <v>0.06034229731844862</v>
+        <v>0.2754453126220149</v>
       </c>
       <c r="H29">
-        <v>0.01353838177728521</v>
+        <v>1.584584586401338E-30</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1604,13 +1604,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0.003024201219943734</v>
+        <v>0.0480546112331508</v>
       </c>
       <c r="G30">
-        <v>0.05639504473926517</v>
+        <v>-0.0655706384836055</v>
       </c>
       <c r="H30">
-        <v>0.02102748905625668</v>
+        <v>0.007281736026034389</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1630,13 +1630,13 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0.03227924000984927</v>
+        <v>0.0729116927865463</v>
       </c>
       <c r="G31">
-        <v>-0.1082585364950464</v>
+        <v>0.1572857083263364</v>
       </c>
       <c r="H31">
-        <v>9.033919250475505E-06</v>
+        <v>9.749783081386951E-11</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1656,13 +1656,13 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>0.0729116927865463</v>
+        <v>0.003024201219943734</v>
       </c>
       <c r="G32">
-        <v>0.1572857083263364</v>
+        <v>0.05639504473926517</v>
       </c>
       <c r="H32">
-        <v>9.749783081386951E-11</v>
+        <v>0.02102748905625668</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1682,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>0.01682115197348555</v>
       </c>
       <c r="G33">
-        <v>0.2482953503862996</v>
+        <v>0.3039142948204692</v>
       </c>
       <c r="H33">
-        <v>6.140762423516477E-25</v>
+        <v>4.16126685706341E-37</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1734,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>0.00658423273262887</v>
+        <v>0.09863902466188534</v>
       </c>
       <c r="G35">
-        <v>-0.1864216878285775</v>
+        <v>0.3892727584110888</v>
       </c>
       <c r="H35">
-        <v>1.481041672950973E-14</v>
+        <v>1.089595289811041E-61</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1760,13 +1760,13 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0.0480546112331508</v>
+        <v>0.03798550812554335</v>
       </c>
       <c r="G36">
-        <v>-0.0655706384836055</v>
+        <v>0.07785472898280013</v>
       </c>
       <c r="H36">
-        <v>0.007281736026034389</v>
+        <v>0.001433344199615437</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1786,13 +1786,13 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0.06094886817812162</v>
+        <v>0.02494677464684747</v>
       </c>
       <c r="G37">
-        <v>-0.07834260227202892</v>
+        <v>0.0755862163968284</v>
       </c>
       <c r="H37">
-        <v>0.001337131558195704</v>
+        <v>0.001970164330603724</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1812,13 +1812,13 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>0.02494677464684747</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0.0755862163968284</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="H38">
-        <v>0.001970164330603724</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1838,13 +1838,13 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>0.02663792909303364</v>
+        <v>0.03227924000984927</v>
       </c>
       <c r="G39">
-        <v>0.03716735259667766</v>
+        <v>-0.1082585364950464</v>
       </c>
       <c r="H39">
-        <v>0.128492223527989</v>
+        <v>9.033919250475505E-06</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1864,13 +1864,13 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>0.06094886817812162</v>
       </c>
       <c r="G40">
-        <v>0.1911693714837015</v>
+        <v>-0.07834260227202892</v>
       </c>
       <c r="H40">
-        <v>3.055303258732452E-15</v>
+        <v>0.001337131558195704</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1916,13 +1916,13 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>0.09863902466188534</v>
+        <v>0.02663792909303364</v>
       </c>
       <c r="G42">
-        <v>0.3892727584110888</v>
+        <v>0.03716735259667766</v>
       </c>
       <c r="H42">
-        <v>1.089595289811041E-61</v>
+        <v>0.128492223527989</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1942,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>0.0665259280122994</v>
+        <v>0.00658423273262887</v>
       </c>
       <c r="G43">
-        <v>0.2754453126220149</v>
+        <v>-0.1864216878285775</v>
       </c>
       <c r="H43">
-        <v>1.584584586401338E-30</v>
+        <v>1.481041672950973E-14</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1968,13 +1968,13 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>0.01682115197348555</v>
+        <v>0.01005952120541931</v>
       </c>
       <c r="G44">
-        <v>0.3039142948204692</v>
+        <v>0.135979414860015</v>
       </c>
       <c r="H44">
-        <v>4.16126685706341E-37</v>
+        <v>2.332423270366468E-08</v>
       </c>
     </row>
   </sheetData>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>0.1244117085663152</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>0.09863902466188534</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>0.09596665305041707</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B6">
         <v>0.09373792849992224</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7">
         <v>0.0729116927865463</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>0.07250003352390966</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <v>0.06789273411413177</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>0.06771094929525123</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>0.06730688815940855</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>0.0665259280122994</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>0.0657404120324192</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0.06352246185843669</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B16">
         <v>0.06094886817812162</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B17">
         <v>0.05203154196427651</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0.04944890453170903</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B19">
         <v>0.0480546112331508</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>0.0406112356812498</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0.03961424326443108</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B22">
         <v>0.03798550812554335</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>0.03469304690640485</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B24">
         <v>0.03227924000984927</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>0.03083395646531173</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>0.03039388235694229</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B28">
         <v>0.02663792909303364</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B29">
         <v>0.02610368711778488</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30">
         <v>0.02494677464684747</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B31">
         <v>0.01785398632339419</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>0.01726766539656444</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B33">
         <v>0.01682115197348555</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34">
         <v>0.01662128920228589</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B35">
         <v>0.01005952120541931</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>0.008979878659193474</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B37">
         <v>0.00658423273262887</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B38">
         <v>0.003864716707023597</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B39">
         <v>0.00322926317430916</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B40">
         <v>0.003024201219943734</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>4342.40411706348</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>1682.290401536478</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>1085.076789541974</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>595.9846117539803</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>558.4367085560835</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>480.0729428774733</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>454.6220680693093</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>447.9616035078638</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B14">
         <v>304.3615276909626</v>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <v>249.5686071976911</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>229.3382156558336</v>
@@ -2771,7 +2771,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B17">
         <v>194.258271392882</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>153.3845763081509</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>130.887968726462</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>83.51115754331592</v>
@@ -2811,7 +2811,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22">
         <v>75.68636973120091</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>72.60456492038352</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B24">
         <v>51.66726992578948</v>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B25">
         <v>51.20380519536801</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26">
         <v>46.8376088705339</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B27">
         <v>43.03454590897858</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B28">
         <v>30.76301699509802</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B29">
         <v>27.17469332567154</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>25.61494581798397</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B31">
         <v>23.51796923824291</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B32">
         <v>21.40264452519091</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B34">
         <v>19.75841772858955</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B35">
         <v>17.69489186968478</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>16.54251136074845</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B37">
         <v>15.43429234615727</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B38">
         <v>15.39444461607886</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39">
         <v>14.94003159495474</v>
@@ -2955,7 +2955,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B40">
         <v>14.57347062388141</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B41">
         <v>12.36219577347118</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B42">
         <v>11.95349113270823</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B43">
         <v>8.395187298679479</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B44">
         <v>6.528992849223204</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B46">
         <v>4.020147437395202</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>753.2485576022657</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>621.1114839490583</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>449.5422950924796</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5">
         <v>380.9823484699023</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B6">
         <v>240.8006187326834</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>188.1819619401369</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>181.3444851068503</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>128.1428541927552</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>116.4829048019989</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B11">
         <v>107.432727539141</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>105.9383924229766</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B13">
         <v>69.89233845381374</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <v>66.41681104582034</v>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>37.4792836704036</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>29.10006429658621</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>22.79280300677015</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19">
         <v>22.23007628110745</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B20">
         <v>14.33108532434674</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B21">
         <v>10.84346846471182</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>10.19234690596405</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B23">
         <v>8.27146775867295</v>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B24">
         <v>5.311883080195145</v>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B25">
         <v>422.0086130676058</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26">
         <v>346.3998473209044</v>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>219.4931181671017</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B28">
         <v>189.79501004315</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B29">
         <v>179.4067717773624</v>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>132.7130497782785</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>128.0659514853349</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B32">
         <v>115.9283817184614</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>107.4216866687169</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B34">
         <v>105.5542712127837</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>69.89089256716291</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B36">
         <v>66.38447548042573</v>
@@ -3417,7 +3417,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>37.43626649035554</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B38">
         <v>27.91863504676936</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B40">
         <v>22.79063724790207</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>21.59055928657702</v>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B42">
         <v>14.30329344853827</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B43">
         <v>10.6718878546015</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44">
         <v>10.0604212294024</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B45">
         <v>8.181182066549855</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B46">
         <v>5.293406540666596</v>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>357.4257975790996</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>189.7942844355019</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B49">
         <v>188.990242631779</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B50">
         <v>179.1814069875248</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B51">
         <v>132.0222523218312</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B52">
         <v>126.1586516393311</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B53">
         <v>104.9230735305154</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B54">
         <v>104.2045795027387</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B55">
         <v>63.41801463944181</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>52.46578351689658</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B57">
         <v>45.495271078065</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B58">
         <v>36.10119196016667</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B59">
         <v>27.75878518411502</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B61">
         <v>21.91736931385755</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B62">
         <v>21.52430363558362</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B63">
         <v>14.30321890244352</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B64">
         <v>10.37576715802304</v>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B65">
         <v>9.997659611193177</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B66">
         <v>7.725803353467899</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B67">
         <v>4.891716487339307</v>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B68">
         <v>350.15876700362</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B69">
         <v>187.2646656777563</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B70">
         <v>131.0438925187317</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B71">
         <v>126.1229198142555</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B72">
         <v>104.8554203896614</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B73">
         <v>104.3542372875243</v>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B74">
         <v>104.0995837087193</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B75">
         <v>62.98166131595279</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B76">
         <v>51.41561844665483</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B77">
         <v>44.37256131248959</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B78">
         <v>36.08640639475832</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B80">
         <v>23.17873712735706</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B81">
         <v>21.82413329779819</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B82">
         <v>20.79939098743634</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B83">
         <v>14.26568970528629</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B84">
         <v>10.23638198844317</v>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B85">
         <v>9.915074446669371</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B86">
         <v>7.32403401602895</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B87">
         <v>4.831489521602753</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B88">
         <v>343.2179446958474</v>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B89">
         <v>125.5077947003103</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B90">
         <v>104.825392379835</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B91">
         <v>102.7342881718347</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B92">
         <v>99.08996399137929</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B93">
         <v>62.8237503697218</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B94">
         <v>46.95493907675103</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B95">
         <v>39.51026475811477</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B96">
         <v>39.0956263428043</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B97">
         <v>36.04227281002906</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B99">
         <v>22.98444763052662</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B100">
         <v>21.81186898247412</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B101">
         <v>20.75482064928144</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B102">
         <v>14.25964084319195</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B103">
         <v>10.17773142116928</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B104">
         <v>9.675462750088085</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B105">
         <v>6.971737396184158</v>
@@ -4176,7 +4176,7 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B106">
         <v>4.817591621498235</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B107">
         <v>325.8334767589092</v>
@@ -4198,7 +4198,7 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B108">
         <v>103.2454978961491</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B109">
         <v>89.07234938360985</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B110">
         <v>61.19465090839606</v>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B111">
         <v>49.39608223071544</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B112">
         <v>46.38481381734387</v>
@@ -4253,7 +4253,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B113">
         <v>38.92800648120138</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B114">
         <v>38.88411173586185</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B115">
         <v>35.88521271312028</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B117">
         <v>22.92479218183164</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B118">
         <v>21.51003779406999</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B119">
         <v>20.7524511151648</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B120">
         <v>12.79881898025029</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B121">
         <v>9.880319222305943</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B122">
         <v>9.60080068653409</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B123">
         <v>6.97106031234692</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B124">
         <v>4.687496588907403</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B125">
         <v>322.6389566022954</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B126">
         <v>88.99783104935011</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B127">
         <v>48.1790112167141</v>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B128">
         <v>45.70723006156884</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B129">
         <v>45.08386262786938</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B130">
         <v>38.85422979982847</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B131">
         <v>38.84650196528916</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B133">
         <v>22.3798010065938</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B134">
         <v>20.3497706928474</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B135">
         <v>16.31257720737751</v>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B136">
         <v>11.82500525076815</v>
@@ -4517,7 +4517,7 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B137">
         <v>9.714837338564061</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B138">
         <v>9.59683858693902</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B139">
         <v>8.399152362778796</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B140">
         <v>6.967033596079141</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B141">
         <v>4.496132212181964</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B142">
         <v>140.1478292398132</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B143">
         <v>44.84253904500241</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B144">
         <v>43.50095480776146</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B145">
         <v>40.29112695258199</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B146">
         <v>38.6006720586165</v>
@@ -4627,7 +4627,7 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B147">
         <v>35.12467116551969</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B148">
         <v>22.16735339425238</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B150">
         <v>19.79668146121563</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B151">
         <v>16.30674433410469</v>
@@ -4682,7 +4682,7 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B152">
         <v>11.76593855010928</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B153">
         <v>9.348473645893128</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B154">
         <v>8.548515166014372</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B155">
         <v>8.382170556852792</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B156">
         <v>6.961559168749637</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B157">
         <v>4.33429996840897</v>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B158">
         <v>129.436329519668</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B159">
         <v>40.68773326028861</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B160">
         <v>38.38608295896825</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B161">
         <v>37.78216414725723</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B162">
         <v>35.11422483991172</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B163">
         <v>22.06799815402378</v>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B165">
         <v>19.5586704774933</v>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B166">
         <v>11.59355630704115</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B167">
         <v>9.278024967226109</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B168">
         <v>8.360673389599295</v>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B169">
         <v>8.320184649648375</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B170">
         <v>6.960425926140306</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B171">
         <v>4.308275164758875</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B172">
         <v>3.496694847179453</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B173">
         <v>38.30554975157519</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B174">
         <v>36.818409209265</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B175">
         <v>34.36782976970145</v>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B176">
         <v>33.41256846109296</v>
@@ -4957,7 +4957,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B177">
         <v>20.93493421373343</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B179">
         <v>19.55064341645915</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B180">
         <v>11.59349759414457</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B181">
         <v>9.152024358088712</v>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B182">
         <v>8.285392754354742</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B183">
         <v>8.236562852304273</v>
@@ -5034,7 +5034,7 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B184">
         <v>4.86969599224304</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B185">
         <v>4.299895480700423</v>
@@ -5056,7 +5056,7 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B186">
         <v>3.460355648131096</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B187">
         <v>33.76069752475988</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B188">
         <v>18.46734346847535</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B189">
         <v>17.6210434341042</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B191">
         <v>15.64017833635289</v>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B192">
         <v>15.36259547621222</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B193">
         <v>11.31393158214105</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B194">
         <v>9.134150411590875</v>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B195">
         <v>8.275924596400808</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B196">
         <v>8.222138054169125</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B197">
         <v>4.299879571629109</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B198">
         <v>4.288901189139285</v>
@@ -5199,7 +5199,7 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B199">
         <v>3.459360250067371</v>
@@ -5210,7 +5210,7 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B200">
         <v>18.17565181127732</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B202">
         <v>17.13118197775876</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B203">
         <v>14.39853703421182</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B204">
         <v>13.48967477870826</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B205">
         <v>9.196729797502988</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B206">
         <v>8.1377404024605</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B207">
         <v>8.106177683033685</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B208">
         <v>7.983058193099758</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B209">
         <v>4.284913595581624</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B210">
         <v>4.155321222230113</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B211">
         <v>2.921413940709789</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B212">
         <v>15.31961240769551</v>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B213">
         <v>13.87521511487681</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B214">
         <v>13.45901133265104</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B215">
         <v>8.983731020786701</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B217">
         <v>8.091616687272305</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B218">
         <v>7.8898703803859</v>
@@ -5419,7 +5419,7 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B219">
         <v>7.524606276423378</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B220">
         <v>4.100611879847337</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B221">
         <v>4.036473394325227</v>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B222">
         <v>2.895520501329768</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B223">
         <v>12.05912487566963</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B224">
         <v>11.69732704581562</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B225">
         <v>8.956269493730833</v>
@@ -5507,7 +5507,7 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B227">
         <v>7.764705303210575</v>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B228">
         <v>7.258695407782731</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B229">
         <v>6.183862547209465</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B230">
         <v>3.928122511751938</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B231">
         <v>3.639712619918944</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B232">
         <v>2.893097787189105</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B233">
         <v>11.47430877943272</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B234">
         <v>7.540077819986799</v>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B235">
         <v>6.758127586816794</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B237">
         <v>5.536584629465203</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B238">
         <v>4.269237442241603</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B239">
         <v>3.635663641156808</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B240">
         <v>3.203374240829735</v>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B241">
         <v>2.88636438870614</v>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>11.47430877943272</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B3">
         <v>7.540077819986799</v>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>6.758127586816794</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>5.536584629465203</v>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>4.269237442241603</v>
@@ -5738,7 +5738,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B8">
         <v>3.635663641156808</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>3.203374240829735</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>2.88636438870614</v>
@@ -5782,42 +5782,42 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/gangnam/feature_selection_summary.xlsx
+++ b/연구코드/results/feature_selection/gangnam/feature_selection_summary.xlsx
@@ -47,7 +47,7 @@
     <t>VIF pruning (VIF&gt;10)</t>
   </si>
   <si>
-    <t>fft_mag_std, wavelet_cA_std, p90, band3_energy, band2_energy_ratio, p95, band1_energy, RMSE, p75, band4_energy, peak_mean_height, AUC, p25, AUC_normalized, band3_energy_ratio, median, band4_energy_ratio, wavelet_cA_energy, mean_abs_deviation, spectral_rolloff</t>
+    <t>band3_energy_ratio, peak_mean_height, fft_mag_std, AUC_normalized, wavelet_cA_energy, spectral_rolloff, mean_abs_deviation, p95, p75, RMSE, AUC, band1_energy, band4_energy_ratio, band2_energy_ratio, p90, wavelet_cA_std, median, band4_energy, band3_energy, p25</t>
   </si>
   <si>
     <t>CV, IQR, band1_energy_ratio, band2_energy, dominant_freq, min, p10, p5, p90_p10_ratio, signal_energy, signal_length, slope_abs_mean, slope_max, slope_mean, slope_std, spectral_energy, spectral_spread, wavelet_cD1_energy, wavelet_cD1_std, wavelet_cD2_energy, wavelet_cD2_std, wavelet_energy_ratio_D1</t>
@@ -71,27 +71,27 @@
     <t>exhaustive_or_SFS_best</t>
   </si>
   <si>
+    <t>vote_ge3</t>
+  </si>
+  <si>
     <t>RFE_only</t>
   </si>
   <si>
-    <t>vote_ge3</t>
+    <t>union_all</t>
+  </si>
+  <si>
+    <t>RF_Perm_only</t>
   </si>
   <si>
     <t>LASSO_only</t>
   </si>
   <si>
+    <t>vote_ge1</t>
+  </si>
+  <si>
     <t>vote_ge2</t>
   </si>
   <si>
-    <t>vote_ge1</t>
-  </si>
-  <si>
-    <t>union_all</t>
-  </si>
-  <si>
-    <t>RF_Perm_only</t>
-  </si>
-  <si>
     <t>CV, IQR, band1_energy_ratio, band2_energy, dominant_freq, max, mean, min, p10, p5, p90_p10_ratio, signal_energy, signal_length, slope_abs_mean, slope_max, slope_mean, slope_min, slope_std, spectral_energy, spectral_spread, std, wavelet_cD1_energy, wavelet_cD1_std, wavelet_cD2_energy, wavelet_cD2_std</t>
   </si>
   <si>
@@ -122,133 +122,133 @@
     <t>p_value</t>
   </si>
   <si>
+    <t>wavelet_cD2_energy</t>
+  </si>
+  <si>
+    <t>dominant_freq</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>IQR</t>
+  </si>
+  <si>
     <t>spectral_spread</t>
   </si>
   <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>band2_energy</t>
+  </si>
+  <si>
+    <t>band1_energy_ratio</t>
+  </si>
+  <si>
+    <t>p90_p10_ratio</t>
+  </si>
+  <si>
+    <t>slope_max</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>wavelet_cD1_energy</t>
+  </si>
+  <si>
+    <t>wavelet_cD1_std</t>
+  </si>
+  <si>
+    <t>wavelet_cD2_std</t>
+  </si>
+  <si>
+    <t>p10</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
     <t>slope_std</t>
   </si>
   <si>
+    <t>slope_mean</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>slope_abs_mean</t>
+  </si>
+  <si>
+    <t>slope_min</t>
+  </si>
+  <si>
     <t>spectral_energy</t>
   </si>
   <si>
-    <t>wavelet_cD2_energy</t>
-  </si>
-  <si>
-    <t>slope_abs_mean</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>p10</t>
-  </si>
-  <si>
     <t>min</t>
   </si>
   <si>
-    <t>dominant_freq</t>
-  </si>
-  <si>
-    <t>slope_mean</t>
-  </si>
-  <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>IQR</t>
-  </si>
-  <si>
-    <t>wavelet_cD1_std</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>p90_p10_ratio</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>band2_energy</t>
-  </si>
-  <si>
-    <t>p5</t>
-  </si>
-  <si>
-    <t>band1_energy_ratio</t>
-  </si>
-  <si>
-    <t>wavelet_cD1_energy</t>
-  </si>
-  <si>
     <t>signal_length</t>
   </si>
   <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_std</t>
-  </si>
-  <si>
-    <t>slope_max</t>
+    <t>peak_max_width</t>
+  </si>
+  <si>
+    <t>wavelet_energy_ratio_D1</t>
+  </si>
+  <si>
+    <t>peak_last_pos</t>
+  </si>
+  <si>
+    <t>fft_mag_max</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
+  </si>
+  <si>
+    <t>valley_count</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>peak_main_pos</t>
+  </si>
+  <si>
+    <t>peak_max_height</t>
+  </si>
+  <si>
+    <t>peak_std_height</t>
+  </si>
+  <si>
+    <t>zero_crossing_rate</t>
   </si>
   <si>
     <t>peak_count</t>
   </si>
   <si>
-    <t>peak_mean_width</t>
-  </si>
-  <si>
-    <t>peak_max_height</t>
-  </si>
-  <si>
-    <t>wavelet_energy_ratio_D1</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
     <t>wavelet_cD3_energy</t>
   </si>
   <si>
-    <t>peak_max_width</t>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
+    <t>first_high_pos</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
+    <t>peak_first_pos</t>
   </si>
   <si>
     <t>skewness</t>
-  </si>
-  <si>
-    <t>kurtosis</t>
-  </si>
-  <si>
-    <t>first_high_pos</t>
-  </si>
-  <si>
-    <t>peak_first_pos</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>peak_std_height</t>
-  </si>
-  <si>
-    <t>peak_last_pos</t>
-  </si>
-  <si>
-    <t>zero_crossing_rate</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
-  </si>
-  <si>
-    <t>fft_mag_max</t>
-  </si>
-  <si>
-    <t>valley_count</t>
   </si>
   <si>
     <t>range</t>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>0.3062584100234444</v>
+        <v>0.3062584100234443</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -747,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>0.3042395298783716</v>
+        <v>0.3042395298783714</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -761,7 +761,7 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>0.2829985661317456</v>
+        <v>0.2829985661317454</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -775,7 +775,7 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>0.2829985661317456</v>
+        <v>0.2829985661317446</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -789,7 +789,7 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>0.2829985661317456</v>
+        <v>0.2829985661317445</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>43</v>
       </c>
       <c r="C8">
-        <v>0.2829985661317455</v>
+        <v>0.2829985661317445</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -817,7 +817,7 @@
         <v>43</v>
       </c>
       <c r="C9">
-        <v>0.2829985661317453</v>
+        <v>0.2829985661317445</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -876,13 +876,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.03039388235694229</v>
       </c>
       <c r="G2">
-        <v>0.07275059108621751</v>
+        <v>0.1008436343579578</v>
       </c>
       <c r="H2">
-        <v>0.00289870113315105</v>
+        <v>3.573892182348782E-05</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,13 +902,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.0406112356812498</v>
+        <v>0.1244117085663152</v>
       </c>
       <c r="G3">
-        <v>0.1577073432284136</v>
+        <v>0.1919972091980031</v>
       </c>
       <c r="H3">
-        <v>8.678327498074129E-11</v>
+        <v>2.310364951717366E-15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0.01726766539656444</v>
+        <v>0.06352246185843669</v>
       </c>
       <c r="G4">
-        <v>-0.07391748849713509</v>
+        <v>0.2110596997711981</v>
       </c>
       <c r="H4">
-        <v>0.002476633652844342</v>
+        <v>2.604705109483967E-18</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -954,13 +954,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.03039388235694229</v>
+        <v>0.03154209489491144</v>
       </c>
       <c r="G5">
-        <v>0.1008436343579578</v>
+        <v>-0.2872726777309642</v>
       </c>
       <c r="H5">
-        <v>3.573892182348782E-05</v>
+        <v>3.611391913251436E-33</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.03083395646531173</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.07771813486143136</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="H6">
-        <v>0.001461402009404134</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1006,13 +1006,13 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.01662128920228589</v>
+        <v>0.09373792849992224</v>
       </c>
       <c r="G7">
-        <v>-0.1433422766507355</v>
+        <v>0.3239516425453906</v>
       </c>
       <c r="H7">
-        <v>3.842190132128082E-09</v>
+        <v>3.342683028581172E-42</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1032,13 +1032,13 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.09596665305041707</v>
+        <v>0.003864716707023597</v>
       </c>
       <c r="G8">
-        <v>-0.3596962663427493</v>
+        <v>-0.01719139192159592</v>
       </c>
       <c r="H8">
-        <v>2.683797095732755E-52</v>
+        <v>0.4821152548824258</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0.06771094929525123</v>
+        <v>0.008979878659193474</v>
       </c>
       <c r="G9">
-        <v>0.3527055263853811</v>
+        <v>-0.08778557438798017</v>
       </c>
       <c r="H9">
-        <v>3.222212217089366E-50</v>
+        <v>0.0003231877396473665</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1084,13 +1084,13 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.03469304690640485</v>
+        <v>0.04944890453170903</v>
       </c>
       <c r="G10">
-        <v>0.2990449750900401</v>
+        <v>-0.3516233652116398</v>
       </c>
       <c r="H10">
-        <v>6.290811487188656E-36</v>
+        <v>6.689389489174903E-50</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1110,13 +1110,13 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.1244117085663152</v>
+        <v>0.01785398632339419</v>
       </c>
       <c r="G11">
-        <v>0.1919972091980031</v>
+        <v>0.07486418638892788</v>
       </c>
       <c r="H11">
-        <v>2.310364951717366E-15</v>
+        <v>0.002176350543611736</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1136,13 +1136,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.00322926317430916</v>
+        <v>0.09596665305041707</v>
       </c>
       <c r="G12">
-        <v>0.1081780747048873</v>
+        <v>-0.3596962663427493</v>
       </c>
       <c r="H12">
-        <v>9.174239567674161E-06</v>
+        <v>2.683797095732755E-52</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0.06352246185843669</v>
+        <v>0.0657404120324192</v>
       </c>
       <c r="G13">
-        <v>0.2110596997711981</v>
+        <v>0.07682973054579313</v>
       </c>
       <c r="H13">
-        <v>2.604705109483967E-18</v>
+        <v>0.00165658229630614</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1188,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0.03154209489491144</v>
+        <v>0.02610368711778488</v>
       </c>
       <c r="G14">
-        <v>-0.2872726777309642</v>
+        <v>0.04347310173721555</v>
       </c>
       <c r="H14">
-        <v>3.611391913251436E-33</v>
+        <v>0.07537196198872829</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1214,13 +1214,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0.02610368711778488</v>
+        <v>0.05203154196427651</v>
       </c>
       <c r="G15">
-        <v>0.04347310173721555</v>
+        <v>0.06941533395191302</v>
       </c>
       <c r="H15">
-        <v>0.07537196198872829</v>
+        <v>0.004491549210741101</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1240,13 +1240,13 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0.06789273411413177</v>
+        <v>0.06771094929525123</v>
       </c>
       <c r="G16">
-        <v>-0.1225321729843732</v>
+        <v>0.3527055263853811</v>
       </c>
       <c r="H16">
-        <v>4.941706043205827E-07</v>
+        <v>3.222212217089366E-50</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1266,13 +1266,13 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0.04944890453170903</v>
+        <v>0.01662128920228589</v>
       </c>
       <c r="G17">
-        <v>-0.3516233652116398</v>
+        <v>-0.1433422766507355</v>
       </c>
       <c r="H17">
-        <v>6.689389489174903E-50</v>
+        <v>3.842190132128082E-09</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1292,13 +1292,13 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0.06730688815940855</v>
+        <v>0.03961424326443108</v>
       </c>
       <c r="G18">
-        <v>0.3064271188370573</v>
+        <v>0.2942299536207652</v>
       </c>
       <c r="H18">
-        <v>1.003867397414242E-37</v>
+        <v>8.767952186342553E-35</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1318,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0.003864716707023597</v>
+        <v>0.0406112356812498</v>
       </c>
       <c r="G19">
-        <v>-0.01719139192159592</v>
+        <v>0.1577073432284136</v>
       </c>
       <c r="H19">
-        <v>0.4821152548824258</v>
+        <v>8.678327498074129E-11</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0.03961424326443108</v>
+        <v>0.00322926317430916</v>
       </c>
       <c r="G20">
-        <v>0.2942299536207652</v>
+        <v>0.1081780747048873</v>
       </c>
       <c r="H20">
-        <v>8.767952186342553E-35</v>
+        <v>9.174239567674161E-06</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1370,13 +1370,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0.008979878659193474</v>
+        <v>0.06730688815940855</v>
       </c>
       <c r="G21">
-        <v>-0.08778557438798017</v>
+        <v>0.3064271188370573</v>
       </c>
       <c r="H21">
-        <v>0.0003231877396473665</v>
+        <v>1.003867397414242E-37</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1396,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.0657404120324192</v>
+        <v>0.03083395646531173</v>
       </c>
       <c r="G22">
-        <v>0.07682973054579313</v>
+        <v>0.07771813486143136</v>
       </c>
       <c r="H22">
-        <v>0.00165658229630614</v>
+        <v>0.001461402009404134</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1422,13 +1422,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0.07250003352390966</v>
+        <v>0.06789273411413177</v>
       </c>
       <c r="G23">
-        <v>0.2510824608572515</v>
+        <v>-0.1225321729843732</v>
       </c>
       <c r="H23">
-        <v>1.756039598366772E-25</v>
+        <v>4.941706043205827E-07</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1448,13 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0.09373792849992224</v>
+        <v>0.01726766539656444</v>
       </c>
       <c r="G24">
-        <v>0.3239516425453906</v>
+        <v>-0.07391748849713509</v>
       </c>
       <c r="H24">
-        <v>3.342683028581172E-42</v>
+        <v>0.002476633652844342</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1474,13 +1474,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0.05203154196427651</v>
+        <v>0.03469304690640485</v>
       </c>
       <c r="G25">
-        <v>0.06941533395191302</v>
+        <v>0.2990449750900401</v>
       </c>
       <c r="H25">
-        <v>0.004491549210741101</v>
+        <v>6.290811487188656E-36</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1500,13 +1500,13 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0.01785398632339419</v>
+        <v>0.07250003352390966</v>
       </c>
       <c r="G26">
-        <v>0.07486418638892788</v>
+        <v>0.2510824608572515</v>
       </c>
       <c r="H26">
-        <v>0.002176350543611736</v>
+        <v>1.756039598366772E-25</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>0.01682115197348555</v>
       </c>
       <c r="G27">
-        <v>0.06034229731844862</v>
+        <v>0.3039142948204692</v>
       </c>
       <c r="H27">
-        <v>0.01353838177728521</v>
+        <v>4.16126685706341E-37</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1552,13 +1552,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>0.0480546112331508</v>
       </c>
       <c r="G28">
-        <v>0.2482953503862996</v>
+        <v>-0.0655706384836055</v>
       </c>
       <c r="H28">
-        <v>6.140762423516477E-25</v>
+        <v>0.007281736026034389</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0.0665259280122994</v>
+        <v>0.06094886817812162</v>
       </c>
       <c r="G29">
-        <v>0.2754453126220149</v>
+        <v>-0.07834260227202892</v>
       </c>
       <c r="H29">
-        <v>1.584584586401338E-30</v>
+        <v>0.001337131558195704</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1604,13 +1604,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0.0480546112331508</v>
+        <v>0.00658423273262887</v>
       </c>
       <c r="G30">
-        <v>-0.0655706384836055</v>
+        <v>-0.1864216878285775</v>
       </c>
       <c r="H30">
-        <v>0.007281736026034389</v>
+        <v>1.481041672950973E-14</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1630,13 +1630,13 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0.0729116927865463</v>
+        <v>0.09863902466188534</v>
       </c>
       <c r="G31">
-        <v>0.1572857083263364</v>
+        <v>0.3892727584110888</v>
       </c>
       <c r="H31">
-        <v>9.749783081386951E-11</v>
+        <v>1.089595289811041E-61</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1656,13 +1656,13 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>0.003024201219943734</v>
+        <v>0.01005952120541931</v>
       </c>
       <c r="G32">
-        <v>0.05639504473926517</v>
+        <v>0.135979414860015</v>
       </c>
       <c r="H32">
-        <v>0.02102748905625668</v>
+        <v>2.332423270366469E-08</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1682,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>0.01682115197348555</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>0.3039142948204692</v>
+        <v>0.2482953503862996</v>
       </c>
       <c r="H33">
-        <v>4.16126685706341E-37</v>
+        <v>6.140762423516477E-25</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1708,13 +1708,13 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0.06971817481055353</v>
+        <v>0.0729116927865463</v>
       </c>
       <c r="G34">
-        <v>-0.3270245433443572</v>
+        <v>0.1572857083263364</v>
       </c>
       <c r="H34">
-        <v>5.101476724101203E-43</v>
+        <v>9.749783081386951E-11</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1734,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>0.09863902466188534</v>
+        <v>0.0665259280122994</v>
       </c>
       <c r="G35">
-        <v>0.3892727584110888</v>
+        <v>0.2754453126220149</v>
       </c>
       <c r="H35">
-        <v>1.089595289811041E-61</v>
+        <v>1.584584586401338E-30</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1760,13 +1760,13 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0.03798550812554335</v>
+        <v>0.03227924000984927</v>
       </c>
       <c r="G36">
-        <v>0.07785472898280013</v>
+        <v>-0.1082585364950464</v>
       </c>
       <c r="H36">
-        <v>0.001433344199615437</v>
+        <v>9.033919250475503E-06</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1786,13 +1786,13 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0.02494677464684747</v>
+        <v>0.1019379054721394</v>
       </c>
       <c r="G37">
-        <v>0.0755862163968284</v>
+        <v>0.2934318753637294</v>
       </c>
       <c r="H37">
-        <v>0.001970164330603724</v>
+        <v>1.350307061696287E-34</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.1911693714837015</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="H38">
-        <v>3.055303258732452E-15</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1838,13 +1838,13 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>0.03227924000984927</v>
+        <v>0.003024201219943734</v>
       </c>
       <c r="G39">
-        <v>-0.1082585364950464</v>
+        <v>0.05639504473926517</v>
       </c>
       <c r="H39">
-        <v>9.033919250475505E-06</v>
+        <v>0.02102748905625668</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1864,13 +1864,13 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>0.06094886817812162</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>-0.07834260227202892</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="H40">
-        <v>0.001337131558195704</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1890,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>0.1019379054721394</v>
+        <v>0.03798550812554335</v>
       </c>
       <c r="G41">
-        <v>0.2934318753637294</v>
+        <v>0.07785472898280013</v>
       </c>
       <c r="H41">
-        <v>1.350307061696287E-34</v>
+        <v>0.001433344199615437</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1942,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>0.00658423273262887</v>
+        <v>0.02494677464684747</v>
       </c>
       <c r="G43">
-        <v>-0.1864216878285775</v>
+        <v>0.0755862163968284</v>
       </c>
       <c r="H43">
-        <v>1.481041672950973E-14</v>
+        <v>0.001970164330603724</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1968,13 +1968,13 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>0.01005952120541931</v>
+        <v>0.06971817481055353</v>
       </c>
       <c r="G44">
-        <v>0.135979414860015</v>
+        <v>-0.3270245433443572</v>
       </c>
       <c r="H44">
-        <v>2.332423270366468E-08</v>
+        <v>5.101476724101203E-43</v>
       </c>
     </row>
   </sheetData>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0.1244117085663152</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>0.1019379054721394</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0.09863902466188534</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>0.09596665305041707</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0.09373792849992224</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B7">
         <v>0.0729116927865463</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B8">
         <v>0.07250003352390966</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9">
         <v>0.06971817481055353</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>0.06789273411413177</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>0.06771094929525123</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>0.06730688815940855</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B13">
         <v>0.0665259280122994</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0.0657404120324192</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>0.06352246185843669</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B16">
         <v>0.06094886817812162</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>0.05203154196427651</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B18">
         <v>0.04944890453170903</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19">
         <v>0.0480546112331508</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0.0406112356812498</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>0.03961424326443108</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B22">
         <v>0.03798550812554335</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>0.03469304690640485</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B24">
         <v>0.03227924000984927</v>
@@ -2320,12 +2320,12 @@
         <v>-0.1082585364950464</v>
       </c>
       <c r="D24">
-        <v>9.033919250475505E-06</v>
+        <v>9.033919250475503E-06</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>0.03154209489491144</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>0.03083395646531173</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0.03039388235694229</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29">
         <v>0.02610368711778488</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B30">
         <v>0.02494677464684747</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>0.01785398632339419</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B32">
         <v>0.01726766539656444</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B33">
         <v>0.01682115197348555</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B34">
         <v>0.01662128920228589</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B35">
         <v>0.01005952120541931</v>
@@ -2474,12 +2474,12 @@
         <v>0.135979414860015</v>
       </c>
       <c r="D35">
-        <v>2.332423270366468E-08</v>
+        <v>2.332423270366469E-08</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B36">
         <v>0.008979878659193474</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B37">
         <v>0.00658423273262887</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>0.003864716707023597</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B39">
         <v>0.00322926317430916</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B40">
         <v>0.003024201219943734</v>
@@ -2549,86 +2549,86 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>-0.009061067721921497</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="D41">
-        <v>0.7110396676887148</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.2482953503862996</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="D42">
-        <v>6.140762423516477E-25</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.06034229731844862</v>
+        <v>-0.009061067721921497</v>
       </c>
       <c r="D43">
-        <v>0.01353838177728521</v>
+        <v>0.7110396676887148</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0.1911693714837015</v>
+        <v>-0.03818823497274026</v>
       </c>
       <c r="D44">
-        <v>3.055303258732452E-15</v>
+        <v>0.1183217145704403</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>-0.03818823497274026</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="D45">
-        <v>0.1183217145704403</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0.07275059108621751</v>
+        <v>0.2482953503862996</v>
       </c>
       <c r="D46">
-        <v>0.00289870113315105</v>
+        <v>6.140762423516477E-25</v>
       </c>
     </row>
   </sheetData>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
@@ -2675,23 +2675,23 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5">
-        <v>4342.40411706348</v>
+        <v>4342.404117067667</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B6">
-        <v>1682.290401536478</v>
+        <v>1682.290401537106</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>1085.076789541974</v>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B8">
-        <v>595.9846117539803</v>
+        <v>595.9846117540986</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2710,36 +2710,36 @@
         <v>77</v>
       </c>
       <c r="B9">
-        <v>566.2138795577548</v>
+        <v>566.2138795586446</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B10">
-        <v>558.4367085560835</v>
+        <v>558.436708557053</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11">
-        <v>480.0729428774733</v>
+        <v>480.0729428775501</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B12">
-        <v>454.6220680693093</v>
+        <v>454.6220680693781</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>447.9616035078638</v>
@@ -2747,23 +2747,23 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14">
-        <v>304.3615276909626</v>
+        <v>304.3615276910346</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B15">
-        <v>249.5686071976911</v>
+        <v>249.5686071977256</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <v>229.3382156558336</v>
@@ -2771,58 +2771,58 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B17">
-        <v>194.258271392882</v>
+        <v>194.2582713928903</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B18">
-        <v>153.3845763081509</v>
+        <v>153.3845763081665</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B19">
-        <v>138.2878417312995</v>
+        <v>138.2878417316179</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20">
-        <v>130.887968726462</v>
+        <v>130.8879687265438</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B21">
-        <v>83.51115754331592</v>
+        <v>83.51115754332133</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B22">
-        <v>75.68636973120091</v>
+        <v>75.68636973166326</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>72.60456492038352</v>
+        <v>72.60456492039522</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2830,183 +2830,183 @@
         <v>73</v>
       </c>
       <c r="B24">
-        <v>51.66726992578948</v>
+        <v>51.66726992580963</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B25">
-        <v>51.20380519536801</v>
+        <v>51.20380519536888</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B26">
-        <v>46.8376088705339</v>
+        <v>46.83760887053438</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B27">
-        <v>43.03454590897858</v>
+        <v>43.03454590898187</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B28">
-        <v>30.76301699509802</v>
+        <v>30.76301699510516</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B29">
-        <v>27.17469332567154</v>
+        <v>27.17469332568114</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B30">
-        <v>25.61494581798397</v>
+        <v>25.61494581798696</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B31">
-        <v>23.51796923824291</v>
+        <v>23.51796923824315</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B32">
-        <v>21.40264452519091</v>
+        <v>21.40264452519152</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B33">
-        <v>19.95387756390497</v>
+        <v>19.95387756392349</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>19.75841772858955</v>
+        <v>19.7584177285912</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B35">
-        <v>17.69489186968478</v>
+        <v>17.69489186969374</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B36">
-        <v>16.54251136074845</v>
+        <v>16.54251136076972</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B37">
-        <v>15.43429234615727</v>
+        <v>15.43429234615746</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B38">
-        <v>15.39444461607886</v>
+        <v>15.39444461608752</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B39">
-        <v>14.94003159495474</v>
+        <v>14.94003159502051</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>14.57347062388141</v>
+        <v>14.57347062388143</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B41">
-        <v>12.36219577347118</v>
+        <v>12.36219577347191</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B42">
-        <v>11.95349113270823</v>
+        <v>11.95349113271388</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B43">
-        <v>8.395187298679479</v>
+        <v>8.395187298679879</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B44">
-        <v>6.528992849223204</v>
+        <v>6.528992849223355</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B45">
-        <v>5.662198183163771</v>
+        <v>5.662198183164302</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B46">
-        <v>4.020147437395202</v>
+        <v>4.020147437396045</v>
       </c>
     </row>
   </sheetData>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>753.2485576022657</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>621.1114839490583</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>449.5422950924796</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>380.9823484699023</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>240.8006187326834</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>188.1819619401369</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>181.3444851068503</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>128.1428541927552</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>116.4829048019989</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>107.432727539141</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>105.9383924229766</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>69.89233845381374</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>66.41681104582034</v>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>37.4792836704036</v>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>30.77188782825023</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <v>29.10006429658621</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>22.79280300677015</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>22.23007628110745</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B20">
         <v>14.33108532434674</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>10.84346846471182</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <v>10.19234690596405</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>8.27146775867295</v>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24">
         <v>5.311883080195145</v>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>422.0086130676058</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B26">
         <v>346.3998473209044</v>
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>219.4931181671017</v>
+        <v>219.4931181670963</v>
       </c>
       <c r="C27">
         <v>22</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28">
         <v>189.79501004315</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B29">
         <v>179.4067717773624</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B30">
-        <v>132.7130497782785</v>
+        <v>132.7130497782766</v>
       </c>
       <c r="C30">
         <v>22</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>128.0659514853349</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B32">
         <v>115.9283817184614</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B33">
         <v>107.4216866687169</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34">
-        <v>105.5542712127837</v>
+        <v>105.554271212785</v>
       </c>
       <c r="C34">
         <v>22</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>69.89089256716291</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>66.38447548042573</v>
@@ -3417,7 +3417,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B37">
         <v>37.43626649035554</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>27.91863504676936</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B39">
-        <v>27.28433132420081</v>
+        <v>27.28433132420089</v>
       </c>
       <c r="C39">
         <v>22</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B40">
         <v>22.79063724790207</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>21.59055928657702</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B42">
-        <v>14.30329344853827</v>
+        <v>14.30329344853825</v>
       </c>
       <c r="C42">
         <v>22</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B43">
         <v>10.6718878546015</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B44">
         <v>10.0604212294024</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>8.181182066549855</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B46">
         <v>5.293406540666596</v>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B47">
         <v>357.4257975790996</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B48">
         <v>189.7942844355019</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B49">
-        <v>188.990242631779</v>
+        <v>188.9902426317829</v>
       </c>
       <c r="C49">
         <v>21</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B50">
         <v>179.1814069875248</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B51">
         <v>132.0222523218312</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B52">
         <v>126.1586516393311</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53">
         <v>104.9230735305154</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B54">
         <v>104.2045795027387</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B55">
         <v>63.41801463944181</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B56">
         <v>52.46578351689658</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B57">
         <v>45.495271078065</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B58">
         <v>36.10119196016667</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B59">
-        <v>27.75878518411502</v>
+        <v>27.75878518411511</v>
       </c>
       <c r="C59">
         <v>21</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B60">
-        <v>27.15714572046898</v>
+        <v>27.15714572046759</v>
       </c>
       <c r="C60">
         <v>21</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B61">
         <v>21.91736931385755</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B62">
         <v>21.52430363558362</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B63">
         <v>14.30321890244352</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B64">
         <v>10.37576715802304</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B65">
-        <v>9.997659611193177</v>
+        <v>9.997659611193187</v>
       </c>
       <c r="C65">
         <v>21</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B66">
         <v>7.725803353467899</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B67">
-        <v>4.891716487339307</v>
+        <v>4.891716487339313</v>
       </c>
       <c r="C67">
         <v>21</v>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B68">
         <v>350.15876700362</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B69">
         <v>187.2646656777563</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B70">
         <v>131.0438925187317</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B71">
         <v>126.1229198142555</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72">
         <v>104.8554203896614</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B73">
         <v>104.3542372875243</v>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B74">
         <v>104.0995837087193</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B75">
         <v>62.98166131595279</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B76">
         <v>51.41561844665483</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B77">
         <v>44.37256131248959</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B78">
         <v>36.08640639475832</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B79">
-        <v>25.96157306980502</v>
+        <v>25.961573069803</v>
       </c>
       <c r="C79">
         <v>20</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B80">
         <v>23.17873712735706</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B81">
         <v>21.82413329779819</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B82">
         <v>20.79939098743634</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B83">
         <v>14.26568970528629</v>
@@ -3934,10 +3934,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B84">
-        <v>10.23638198844317</v>
+        <v>10.23638198844316</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B85">
-        <v>9.915074446669371</v>
+        <v>9.91507444666936</v>
       </c>
       <c r="C85">
         <v>20</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B86">
         <v>7.32403401602895</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B87">
         <v>4.831489521602753</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B88">
         <v>343.2179446958474</v>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B89">
         <v>125.5077947003103</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B90">
         <v>104.825392379835</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B91">
         <v>102.7342881718347</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B92">
         <v>99.08996399137929</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B93">
         <v>62.8237503697218</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B94">
         <v>46.95493907675103</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B95">
         <v>39.51026475811477</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B96">
-        <v>39.0956263428043</v>
+        <v>39.0956263428038</v>
       </c>
       <c r="C96">
         <v>19</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B97">
         <v>36.04227281002906</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B98">
-        <v>24.14425539597859</v>
+        <v>24.14425539597872</v>
       </c>
       <c r="C98">
         <v>19</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B99">
         <v>22.98444763052662</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B100">
         <v>21.81186898247412</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B101">
         <v>20.75482064928144</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B102">
         <v>14.25964084319195</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B103">
         <v>10.17773142116928</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B104">
-        <v>9.675462750088085</v>
+        <v>9.675462750088021</v>
       </c>
       <c r="C104">
         <v>19</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B105">
         <v>6.971737396184158</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B106">
-        <v>4.817591621498235</v>
+        <v>4.817591621498238</v>
       </c>
       <c r="C106">
         <v>19</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B107">
         <v>325.8334767589092</v>
@@ -4198,7 +4198,7 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B108">
         <v>103.2454978961491</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B109">
         <v>89.07234938360985</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B110">
         <v>61.19465090839606</v>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B111">
         <v>49.39608223071544</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B112">
         <v>46.38481381734387</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B113">
-        <v>38.92800648120138</v>
+        <v>38.92800648120037</v>
       </c>
       <c r="C113">
         <v>18</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B114">
         <v>38.88411173586185</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B115">
         <v>35.88521271312028</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B116">
-        <v>23.18050670244102</v>
+        <v>23.18050670244269</v>
       </c>
       <c r="C116">
         <v>18</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B117">
         <v>22.92479218183164</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B118">
-        <v>21.51003779406999</v>
+        <v>21.51003779407004</v>
       </c>
       <c r="C118">
         <v>18</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B119">
         <v>20.7524511151648</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B120">
         <v>12.79881898025029</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B121">
         <v>9.880319222305943</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B122">
-        <v>9.60080068653409</v>
+        <v>9.600800686534079</v>
       </c>
       <c r="C122">
         <v>18</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B123">
         <v>6.97106031234692</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B124">
         <v>4.687496588907403</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B125">
         <v>322.6389566022954</v>
@@ -4396,10 +4396,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B126">
-        <v>88.99783104935011</v>
+        <v>88.99783104935099</v>
       </c>
       <c r="C126">
         <v>17</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B127">
         <v>48.1790112167141</v>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B128">
         <v>45.70723006156884</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B129">
         <v>45.08386262786938</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B130">
         <v>38.85422979982847</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B131">
-        <v>38.84650196528916</v>
+        <v>38.84650196528849</v>
       </c>
       <c r="C131">
         <v>17</v>
@@ -4462,10 +4462,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B132">
-        <v>23.01099218714343</v>
+        <v>23.0109921871439</v>
       </c>
       <c r="C132">
         <v>17</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B133">
         <v>22.3798010065938</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B134">
         <v>20.3497706928474</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B135">
         <v>16.31257720737751</v>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B136">
         <v>11.82500525076815</v>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B137">
-        <v>9.714837338564061</v>
+        <v>9.714837338564072</v>
       </c>
       <c r="C137">
         <v>17</v>
@@ -4528,10 +4528,10 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B138">
-        <v>9.59683858693902</v>
+        <v>9.596838586938988</v>
       </c>
       <c r="C138">
         <v>17</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B139">
         <v>8.399152362778796</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B140">
         <v>6.967033596079141</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B141">
-        <v>4.496132212181964</v>
+        <v>4.496132212181966</v>
       </c>
       <c r="C141">
         <v>17</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B142">
         <v>140.1478292398132</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B143">
         <v>44.84253904500241</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B144">
         <v>43.50095480776146</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B145">
         <v>40.29112695258199</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B146">
         <v>38.6006720586165</v>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B147">
-        <v>35.12467116551969</v>
+        <v>35.12467116551955</v>
       </c>
       <c r="C147">
         <v>16</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B148">
         <v>22.16735339425238</v>
@@ -4649,10 +4649,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B149">
-        <v>20.28931570756229</v>
+        <v>20.28931570756037</v>
       </c>
       <c r="C149">
         <v>16</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B150">
         <v>19.79668146121563</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B151">
         <v>16.30674433410469</v>
@@ -4682,7 +4682,7 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B152">
         <v>11.76593855010928</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B153">
         <v>9.348473645893128</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B154">
-        <v>8.548515166014372</v>
+        <v>8.548515166014315</v>
       </c>
       <c r="C154">
         <v>16</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B155">
         <v>8.382170556852792</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B156">
         <v>6.961559168749637</v>
@@ -4737,10 +4737,10 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B157">
-        <v>4.33429996840897</v>
+        <v>4.334299968408972</v>
       </c>
       <c r="C157">
         <v>16</v>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B158">
         <v>129.436329519668</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B159">
         <v>40.68773326028861</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B160">
         <v>38.38608295896825</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B161">
         <v>37.78216414725723</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B162">
-        <v>35.11422483991172</v>
+        <v>35.11422483991199</v>
       </c>
       <c r="C162">
         <v>15</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B163">
         <v>22.06799815402378</v>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B164">
-        <v>20.25288361463705</v>
+        <v>20.25288361463828</v>
       </c>
       <c r="C164">
         <v>15</v>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B165">
         <v>19.5586704774933</v>
@@ -4836,10 +4836,10 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B166">
-        <v>11.59355630704115</v>
+        <v>11.59355630704117</v>
       </c>
       <c r="C166">
         <v>15</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B167">
         <v>9.278024967226109</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B168">
-        <v>8.360673389599295</v>
+        <v>8.36067338959918</v>
       </c>
       <c r="C168">
         <v>15</v>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B169">
-        <v>8.320184649648375</v>
+        <v>8.320184649648382</v>
       </c>
       <c r="C169">
         <v>15</v>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B170">
-        <v>6.960425926140306</v>
+        <v>6.960425926140311</v>
       </c>
       <c r="C170">
         <v>15</v>
@@ -4891,10 +4891,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B171">
-        <v>4.308275164758875</v>
+        <v>4.30827516475888</v>
       </c>
       <c r="C171">
         <v>15</v>
@@ -4902,10 +4902,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B172">
-        <v>3.496694847179453</v>
+        <v>3.496694847179452</v>
       </c>
       <c r="C172">
         <v>15</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B173">
         <v>38.30554975157519</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B174">
         <v>36.818409209265</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B175">
         <v>34.36782976970145</v>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B176">
         <v>33.41256846109296</v>
@@ -4957,7 +4957,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B177">
         <v>20.93493421373343</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B178">
         <v>19.67072465141573</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B179">
         <v>19.55064341645915</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B180">
         <v>11.59349759414457</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B181">
         <v>9.152024358088712</v>
@@ -5012,10 +5012,10 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B182">
-        <v>8.285392754354742</v>
+        <v>8.285392754354749</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B183">
         <v>8.236562852304273</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B184">
-        <v>4.86969599224304</v>
+        <v>4.869695992243043</v>
       </c>
       <c r="C184">
         <v>14</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B185">
         <v>4.299895480700423</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B186">
-        <v>3.460355648131096</v>
+        <v>3.460355648131094</v>
       </c>
       <c r="C186">
         <v>14</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B187">
         <v>33.76069752475988</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B188">
         <v>18.46734346847535</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B189">
         <v>17.6210434341042</v>
@@ -5100,7 +5100,7 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B190">
         <v>17.59158649310429</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B191">
-        <v>15.64017833635289</v>
+        <v>15.64017833635287</v>
       </c>
       <c r="C191">
         <v>13</v>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B192">
         <v>15.36259547621222</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B193">
         <v>11.31393158214105</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B194">
         <v>9.134150411590875</v>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B195">
         <v>8.275924596400808</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B196">
         <v>8.222138054169125</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B197">
-        <v>4.299879571629109</v>
+        <v>4.299879571629114</v>
       </c>
       <c r="C197">
         <v>13</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B198">
-        <v>4.288901189139285</v>
+        <v>4.288901189139287</v>
       </c>
       <c r="C198">
         <v>13</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B199">
-        <v>3.459360250067371</v>
+        <v>3.459360250067372</v>
       </c>
       <c r="C199">
         <v>13</v>
@@ -5210,10 +5210,10 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B200">
-        <v>18.17565181127732</v>
+        <v>18.17565181127735</v>
       </c>
       <c r="C200">
         <v>12</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B201">
-        <v>17.40673623527648</v>
+        <v>17.40673623527652</v>
       </c>
       <c r="C201">
         <v>12</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B202">
         <v>17.13118197775876</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B203">
         <v>14.39853703421182</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B204">
         <v>13.48967477870826</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B205">
         <v>9.196729797502988</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B206">
         <v>8.1377404024605</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B207">
         <v>8.106177683033685</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B208">
         <v>7.983058193099758</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B209">
         <v>4.284913595581624</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B210">
-        <v>4.155321222230113</v>
+        <v>4.155321222230115</v>
       </c>
       <c r="C210">
         <v>12</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B211">
-        <v>2.921413940709789</v>
+        <v>2.921413940709788</v>
       </c>
       <c r="C211">
         <v>12</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B212">
         <v>15.31961240769551</v>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B213">
         <v>13.87521511487681</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B214">
         <v>13.45901133265104</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B215">
         <v>8.983731020786701</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B216">
-        <v>8.553962594638225</v>
+        <v>8.553962594638444</v>
       </c>
       <c r="C216">
         <v>11</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B217">
-        <v>8.091616687272305</v>
+        <v>8.091616687276078</v>
       </c>
       <c r="C217">
         <v>11</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B218">
         <v>7.8898703803859</v>
@@ -5419,7 +5419,7 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B219">
         <v>7.524606276423378</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B220">
         <v>4.100611879847337</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B221">
         <v>4.036473394325227</v>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B222">
         <v>2.895520501329768</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B223">
         <v>12.05912487566963</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B224">
         <v>11.69732704581562</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B225">
         <v>8.956269493730833</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B226">
-        <v>8.469975057611229</v>
+        <v>8.46997505761181</v>
       </c>
       <c r="C226">
         <v>10</v>
@@ -5507,10 +5507,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B227">
-        <v>7.764705303210575</v>
+        <v>7.764705303209216</v>
       </c>
       <c r="C227">
         <v>10</v>
@@ -5518,10 +5518,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B228">
-        <v>7.258695407782731</v>
+        <v>7.258695407782738</v>
       </c>
       <c r="C228">
         <v>10</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B229">
         <v>6.183862547209465</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B230">
         <v>3.928122511751938</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B231">
         <v>3.639712619918944</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B232">
         <v>2.893097787189105</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B233">
         <v>11.47430877943272</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B234">
         <v>7.540077819986799</v>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B235">
         <v>6.758127586816794</v>
@@ -5606,10 +5606,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B236">
-        <v>5.611296802159213</v>
+        <v>5.611296802160668</v>
       </c>
       <c r="C236">
         <v>9</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B237">
         <v>5.536584629465203</v>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B238">
-        <v>4.269237442241603</v>
+        <v>4.269237442242018</v>
       </c>
       <c r="C238">
         <v>9</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B239">
         <v>3.635663641156808</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B240">
         <v>3.203374240829735</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B241">
-        <v>2.88636438870614</v>
+        <v>2.886364388706139</v>
       </c>
       <c r="C241">
         <v>9</v>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>11.47430877943272</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>7.540077819986799</v>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>6.758127586816794</v>
@@ -5714,15 +5714,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>5.611296802159213</v>
+        <v>5.611296802160668</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>5.536584629465203</v>
@@ -5730,15 +5730,15 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B7">
-        <v>4.269237442241603</v>
+        <v>4.269237442242018</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>3.635663641156808</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B9">
         <v>3.203374240829735</v>
@@ -5754,10 +5754,10 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>2.88636438870614</v>
+        <v>2.886364388706139</v>
       </c>
     </row>
   </sheetData>
@@ -5777,47 +5777,47 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/gangnam/feature_selection_summary.xlsx
+++ b/연구코드/results/feature_selection/gangnam/feature_selection_summary.xlsx
@@ -47,7 +47,7 @@
     <t>VIF pruning (VIF&gt;10)</t>
   </si>
   <si>
-    <t>band3_energy_ratio, peak_mean_height, fft_mag_std, AUC_normalized, wavelet_cA_energy, spectral_rolloff, mean_abs_deviation, p95, p75, RMSE, AUC, band1_energy, band4_energy_ratio, band2_energy_ratio, p90, wavelet_cA_std, median, band4_energy, band3_energy, p25</t>
+    <t>peak_mean_height, band4_energy_ratio, band3_energy, median, fft_mag_std, p75, wavelet_cA_std, mean_abs_deviation, band3_energy_ratio, p95, AUC_normalized, p25, band4_energy, spectral_rolloff, RMSE, wavelet_cA_energy, band2_energy_ratio, band1_energy, p90, AUC</t>
   </si>
   <si>
     <t>CV, IQR, band1_energy_ratio, band2_energy, dominant_freq, min, p10, p5, p90_p10_ratio, signal_energy, signal_length, slope_abs_mean, slope_max, slope_mean, slope_std, spectral_energy, spectral_spread, wavelet_cD1_energy, wavelet_cD1_std, wavelet_cD2_energy, wavelet_cD2_std, wavelet_energy_ratio_D1</t>
@@ -77,21 +77,21 @@
     <t>RFE_only</t>
   </si>
   <si>
+    <t>LASSO_only</t>
+  </si>
+  <si>
+    <t>vote_ge2</t>
+  </si>
+  <si>
+    <t>vote_ge1</t>
+  </si>
+  <si>
+    <t>RF_Perm_only</t>
+  </si>
+  <si>
     <t>union_all</t>
   </si>
   <si>
-    <t>RF_Perm_only</t>
-  </si>
-  <si>
-    <t>LASSO_only</t>
-  </si>
-  <si>
-    <t>vote_ge1</t>
-  </si>
-  <si>
-    <t>vote_ge2</t>
-  </si>
-  <si>
     <t>CV, IQR, band1_energy_ratio, band2_energy, dominant_freq, max, mean, min, p10, p5, p90_p10_ratio, signal_energy, signal_length, slope_abs_mean, slope_max, slope_mean, slope_min, slope_std, spectral_energy, spectral_spread, std, wavelet_cD1_energy, wavelet_cD1_std, wavelet_cD2_energy, wavelet_cD2_std</t>
   </si>
   <si>
@@ -122,130 +122,130 @@
     <t>p_value</t>
   </si>
   <si>
+    <t>slope_std</t>
+  </si>
+  <si>
+    <t>slope_max</t>
+  </si>
+  <si>
+    <t>p10</t>
+  </si>
+  <si>
+    <t>signal_length</t>
+  </si>
+  <si>
+    <t>slope_mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
+    <t>slope_min</t>
+  </si>
+  <si>
+    <t>p90_p10_ratio</t>
+  </si>
+  <si>
+    <t>spectral_energy</t>
+  </si>
+  <si>
+    <t>slope_abs_mean</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>band1_energy_ratio</t>
+  </si>
+  <si>
+    <t>wavelet_cD1_energy</t>
+  </si>
+  <si>
+    <t>band2_energy</t>
+  </si>
+  <si>
+    <t>wavelet_cD2_std</t>
+  </si>
+  <si>
     <t>wavelet_cD2_energy</t>
   </si>
   <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>IQR</t>
+  </si>
+  <si>
+    <t>wavelet_cD1_std</t>
+  </si>
+  <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
     <t>dominant_freq</t>
   </si>
   <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>IQR</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>band2_energy</t>
-  </si>
-  <si>
-    <t>band1_energy_ratio</t>
-  </si>
-  <si>
-    <t>p90_p10_ratio</t>
-  </si>
-  <si>
-    <t>slope_max</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>wavelet_cD1_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD1_std</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_std</t>
-  </si>
-  <si>
-    <t>p10</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>p5</t>
-  </si>
-  <si>
-    <t>slope_std</t>
-  </si>
-  <si>
-    <t>slope_mean</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>slope_abs_mean</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>spectral_energy</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>signal_length</t>
+    <t>fft_mag_max</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
+    <t>peak_first_pos</t>
+  </si>
+  <si>
+    <t>valley_count</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
+  </si>
+  <si>
+    <t>zero_crossing_rate</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>peak_last_pos</t>
+  </si>
+  <si>
+    <t>peak_max_height</t>
+  </si>
+  <si>
+    <t>peak_count</t>
   </si>
   <si>
     <t>peak_max_width</t>
   </si>
   <si>
+    <t>peak_main_pos</t>
+  </si>
+  <si>
+    <t>peak_std_height</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_energy</t>
+  </si>
+  <si>
+    <t>first_high_pos</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
     <t>wavelet_energy_ratio_D1</t>
-  </si>
-  <si>
-    <t>peak_last_pos</t>
-  </si>
-  <si>
-    <t>fft_mag_max</t>
-  </si>
-  <si>
-    <t>kurtosis</t>
-  </si>
-  <si>
-    <t>valley_count</t>
-  </si>
-  <si>
-    <t>peak_mean_width</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
-    <t>peak_max_height</t>
-  </si>
-  <si>
-    <t>peak_std_height</t>
-  </si>
-  <si>
-    <t>zero_crossing_rate</t>
-  </si>
-  <si>
-    <t>peak_count</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_energy</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>first_high_pos</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
-  </si>
-  <si>
-    <t>peak_first_pos</t>
   </si>
   <si>
     <t>skewness</t>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>0.3062584100234443</v>
+        <v>0.3062584100234441</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -733,7 +733,7 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>0.3042395298783716</v>
+        <v>0.3042395298783715</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -761,7 +761,7 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>0.2829985661317454</v>
+        <v>0.2829985661317453</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -775,7 +775,7 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>0.2829985661317446</v>
+        <v>0.2829985661317453</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -789,7 +789,7 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>0.2829985661317445</v>
+        <v>0.2829985661317453</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>43</v>
       </c>
       <c r="C8">
-        <v>0.2829985661317445</v>
+        <v>0.282998566131745</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -817,7 +817,7 @@
         <v>43</v>
       </c>
       <c r="C9">
-        <v>0.2829985661317445</v>
+        <v>0.2829985661317446</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -876,13 +876,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.03039388235694229</v>
+        <v>0.0406112356812498</v>
       </c>
       <c r="G2">
-        <v>0.1008436343579578</v>
+        <v>0.1577073432284136</v>
       </c>
       <c r="H2">
-        <v>3.573892182348782E-05</v>
+        <v>8.678327498074129E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,13 +902,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.1244117085663152</v>
+        <v>0.01785398632339419</v>
       </c>
       <c r="G3">
-        <v>0.1919972091980031</v>
+        <v>0.07486418638892788</v>
       </c>
       <c r="H3">
-        <v>2.310364951717366E-15</v>
+        <v>0.002176350543611736</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0.06352246185843669</v>
+        <v>0.06771094929525123</v>
       </c>
       <c r="G4">
-        <v>0.2110596997711981</v>
+        <v>0.3527055263853811</v>
       </c>
       <c r="H4">
-        <v>2.604705109483967E-18</v>
+        <v>3.222212217089366E-50</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -954,13 +954,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.03154209489491144</v>
+        <v>0.07250003352390966</v>
       </c>
       <c r="G5">
-        <v>-0.2872726777309642</v>
+        <v>0.2510824608572515</v>
       </c>
       <c r="H5">
-        <v>3.611391913251436E-33</v>
+        <v>1.756039598366772E-25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.00322926317430916</v>
       </c>
       <c r="G6">
-        <v>0.07275059108621751</v>
+        <v>0.1081780747048873</v>
       </c>
       <c r="H6">
-        <v>0.00289870113315105</v>
+        <v>9.174239567674161E-06</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1006,13 +1006,13 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.09373792849992224</v>
+        <v>0.06352246185843669</v>
       </c>
       <c r="G7">
-        <v>0.3239516425453906</v>
+        <v>0.2110596997711981</v>
       </c>
       <c r="H7">
-        <v>3.342683028581172E-42</v>
+        <v>2.604705109483967E-18</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1032,13 +1032,13 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.003864716707023597</v>
+        <v>0.03961424326443108</v>
       </c>
       <c r="G8">
-        <v>-0.01719139192159592</v>
+        <v>0.2942299536207652</v>
       </c>
       <c r="H8">
-        <v>0.4821152548824258</v>
+        <v>8.767952186342553E-35</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0.008979878659193474</v>
+        <v>0.06789273411413177</v>
       </c>
       <c r="G9">
-        <v>-0.08778557438798017</v>
+        <v>-0.1225321729843732</v>
       </c>
       <c r="H9">
-        <v>0.0003231877396473665</v>
+        <v>4.941706043205827E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1110,13 +1110,13 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.01785398632339419</v>
+        <v>0.01726766539656444</v>
       </c>
       <c r="G11">
-        <v>0.07486418638892788</v>
+        <v>-0.07391748849713509</v>
       </c>
       <c r="H11">
-        <v>0.002176350543611736</v>
+        <v>0.002476633652844342</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1136,13 +1136,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.09596665305041707</v>
+        <v>0.03083395646531173</v>
       </c>
       <c r="G12">
-        <v>-0.3596962663427493</v>
+        <v>0.07771813486143136</v>
       </c>
       <c r="H12">
-        <v>2.683797095732755E-52</v>
+        <v>0.001461402009404134</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0.0657404120324192</v>
+        <v>0.09596665305041707</v>
       </c>
       <c r="G13">
-        <v>0.07682973054579313</v>
+        <v>-0.3596962663427493</v>
       </c>
       <c r="H13">
-        <v>0.00165658229630614</v>
+        <v>2.683797095732755E-52</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1188,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0.02610368711778488</v>
+        <v>0.01662128920228589</v>
       </c>
       <c r="G14">
-        <v>0.04347310173721555</v>
+        <v>-0.1433422766507355</v>
       </c>
       <c r="H14">
-        <v>0.07537196198872829</v>
+        <v>3.842190132128082E-09</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1214,13 +1214,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0.05203154196427651</v>
+        <v>0.09373792849992224</v>
       </c>
       <c r="G15">
-        <v>0.06941533395191302</v>
+        <v>0.3239516425453906</v>
       </c>
       <c r="H15">
-        <v>0.004491549210741101</v>
+        <v>3.342683028581172E-42</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1240,13 +1240,13 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0.06771094929525123</v>
+        <v>0.008979878659193474</v>
       </c>
       <c r="G16">
-        <v>0.3527055263853811</v>
+        <v>-0.08778557438798017</v>
       </c>
       <c r="H16">
-        <v>3.222212217089366E-50</v>
+        <v>0.0003231877396473665</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1266,13 +1266,13 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0.01662128920228589</v>
+        <v>0.0657404120324192</v>
       </c>
       <c r="G17">
-        <v>-0.1433422766507355</v>
+        <v>0.07682973054579313</v>
       </c>
       <c r="H17">
-        <v>3.842190132128082E-09</v>
+        <v>0.00165658229630614</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1292,13 +1292,13 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0.03961424326443108</v>
+        <v>0.003864716707023597</v>
       </c>
       <c r="G18">
-        <v>0.2942299536207652</v>
+        <v>-0.01719139192159592</v>
       </c>
       <c r="H18">
-        <v>8.767952186342553E-35</v>
+        <v>0.4821152548824258</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1318,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0.0406112356812498</v>
+        <v>0.05203154196427651</v>
       </c>
       <c r="G19">
-        <v>0.1577073432284136</v>
+        <v>0.06941533395191302</v>
       </c>
       <c r="H19">
-        <v>8.678327498074129E-11</v>
+        <v>0.004491549210741101</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0.00322926317430916</v>
+        <v>0.03039388235694229</v>
       </c>
       <c r="G20">
-        <v>0.1081780747048873</v>
+        <v>0.1008436343579578</v>
       </c>
       <c r="H20">
-        <v>9.174239567674161E-06</v>
+        <v>3.573892182348782E-05</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1370,13 +1370,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0.06730688815940855</v>
+        <v>0.03469304690640485</v>
       </c>
       <c r="G21">
-        <v>0.3064271188370573</v>
+        <v>0.2990449750900401</v>
       </c>
       <c r="H21">
-        <v>1.003867397414242E-37</v>
+        <v>6.290811487188656E-36</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1396,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.03083395646531173</v>
+        <v>0.03154209489491144</v>
       </c>
       <c r="G22">
-        <v>0.07771813486143136</v>
+        <v>-0.2872726777309642</v>
       </c>
       <c r="H22">
-        <v>0.001461402009404134</v>
+        <v>3.611391913251436E-33</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1422,13 +1422,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0.06789273411413177</v>
+        <v>0.02610368711778488</v>
       </c>
       <c r="G23">
-        <v>-0.1225321729843732</v>
+        <v>0.04347310173721555</v>
       </c>
       <c r="H23">
-        <v>4.941706043205827E-07</v>
+        <v>0.07537196198872829</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1448,13 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0.01726766539656444</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>-0.07391748849713509</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="H24">
-        <v>0.002476633652844342</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1474,13 +1474,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0.03469304690640485</v>
+        <v>0.06730688815940855</v>
       </c>
       <c r="G25">
-        <v>0.2990449750900401</v>
+        <v>0.3064271188370573</v>
       </c>
       <c r="H25">
-        <v>6.290811487188656E-36</v>
+        <v>1.003867397414242E-37</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1500,13 +1500,13 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0.07250003352390966</v>
+        <v>0.1244117085663152</v>
       </c>
       <c r="G26">
-        <v>0.2510824608572515</v>
+        <v>0.1919972091980031</v>
       </c>
       <c r="H26">
-        <v>1.756039598366772E-25</v>
+        <v>2.310364951717366E-15</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>0.01682115197348555</v>
+        <v>0.00658423273262887</v>
       </c>
       <c r="G27">
-        <v>0.3039142948204692</v>
+        <v>-0.1864216878285775</v>
       </c>
       <c r="H27">
-        <v>4.16126685706341E-37</v>
+        <v>1.481041672950973E-14</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1552,13 +1552,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0.0480546112331508</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>-0.0655706384836055</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="H28">
-        <v>0.007281736026034389</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0.06094886817812162</v>
+        <v>0.02494677464684747</v>
       </c>
       <c r="G29">
-        <v>-0.07834260227202892</v>
+        <v>0.0755862163968284</v>
       </c>
       <c r="H29">
-        <v>0.001337131558195704</v>
+        <v>0.001970164330603724</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1604,13 +1604,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0.00658423273262887</v>
+        <v>0.01005952120541931</v>
       </c>
       <c r="G30">
-        <v>-0.1864216878285775</v>
+        <v>0.135979414860015</v>
       </c>
       <c r="H30">
-        <v>1.481041672950973E-14</v>
+        <v>2.332423270366468E-08</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1656,13 +1656,13 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>0.01005952120541931</v>
+        <v>0.1019379054721394</v>
       </c>
       <c r="G32">
-        <v>0.135979414860015</v>
+        <v>0.2934318753637294</v>
       </c>
       <c r="H32">
-        <v>2.332423270366469E-08</v>
+        <v>1.350307061696287E-34</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1708,13 +1708,13 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0.0729116927865463</v>
+        <v>0.06094886817812162</v>
       </c>
       <c r="G34">
-        <v>0.1572857083263364</v>
+        <v>-0.07834260227202892</v>
       </c>
       <c r="H34">
-        <v>9.749783081386951E-11</v>
+        <v>0.001337131558195704</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1760,13 +1760,13 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0.03227924000984927</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>-0.1082585364950464</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="H36">
-        <v>9.033919250475503E-06</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1786,13 +1786,13 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0.1019379054721394</v>
+        <v>0.01682115197348555</v>
       </c>
       <c r="G37">
-        <v>0.2934318753637294</v>
+        <v>0.3039142948204692</v>
       </c>
       <c r="H37">
-        <v>1.350307061696287E-34</v>
+        <v>4.16126685706341E-37</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1812,13 +1812,13 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>0.0729116927865463</v>
       </c>
       <c r="G38">
-        <v>0.06034229731844862</v>
+        <v>0.1572857083263364</v>
       </c>
       <c r="H38">
-        <v>0.01353838177728521</v>
+        <v>9.749783081386951E-11</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1838,13 +1838,13 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>0.003024201219943734</v>
+        <v>0.03227924000984927</v>
       </c>
       <c r="G39">
-        <v>0.05639504473926517</v>
+        <v>-0.1082585364950464</v>
       </c>
       <c r="H39">
-        <v>0.02102748905625668</v>
+        <v>9.033919250475505E-06</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1864,13 +1864,13 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>0.003024201219943734</v>
       </c>
       <c r="G40">
-        <v>0.1911693714837015</v>
+        <v>0.05639504473926517</v>
       </c>
       <c r="H40">
-        <v>3.055303258732452E-15</v>
+        <v>0.02102748905625668</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1942,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>0.02494677464684747</v>
+        <v>0.0480546112331508</v>
       </c>
       <c r="G43">
-        <v>0.0755862163968284</v>
+        <v>-0.0655706384836055</v>
       </c>
       <c r="H43">
-        <v>0.001970164330603724</v>
+        <v>0.007281736026034389</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2003,7 +2003,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <v>0.1244117085663152</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>0.1019379054721394</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>0.09596665305041707</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>0.09373792849992224</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>0.0729116927865463</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0.07250003352390966</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0.06789273411413177</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>0.06771094929525123</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>0.06730688815940855</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>0.0657404120324192</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B15">
         <v>0.06352246185843669</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <v>0.06094886817812162</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>0.05203154196427651</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B19">
         <v>0.0480546112331508</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>0.0406112356812498</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>0.03961424326443108</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>0.03469304690640485</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B24">
         <v>0.03227924000984927</v>
@@ -2320,12 +2320,12 @@
         <v>-0.1082585364950464</v>
       </c>
       <c r="D24">
-        <v>9.033919250475503E-06</v>
+        <v>9.033919250475505E-06</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B25">
         <v>0.03154209489491144</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>0.03083395646531173</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B27">
         <v>0.03039388235694229</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B29">
         <v>0.02610368711778488</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B30">
         <v>0.02494677464684747</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>0.01785398632339419</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>0.01726766539656444</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B33">
         <v>0.01682115197348555</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>0.01662128920228589</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B35">
         <v>0.01005952120541931</v>
@@ -2474,12 +2474,12 @@
         <v>0.135979414860015</v>
       </c>
       <c r="D35">
-        <v>2.332423270366469E-08</v>
+        <v>2.332423270366468E-08</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>0.008979878659193474</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B37">
         <v>0.00658423273262887</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B38">
         <v>0.003864716707023597</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B39">
         <v>0.00322926317430916</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B40">
         <v>0.003024201219943734</v>
@@ -2549,86 +2549,86 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.07275059108621751</v>
+        <v>-0.009061067721921497</v>
       </c>
       <c r="D41">
-        <v>0.00289870113315105</v>
+        <v>0.7110396676887148</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.1911693714837015</v>
+        <v>0.2482953503862996</v>
       </c>
       <c r="D42">
-        <v>3.055303258732452E-15</v>
+        <v>6.140762423516477E-25</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>-0.009061067721921497</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="D43">
-        <v>0.7110396676887148</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>-0.03818823497274026</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="D44">
-        <v>0.1183217145704403</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>0.06034229731844862</v>
+        <v>-0.03818823497274026</v>
       </c>
       <c r="D45">
-        <v>0.01353838177728521</v>
+        <v>0.1183217145704403</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0.2482953503862996</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="D46">
-        <v>6.140762423516477E-25</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
   </sheetData>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
@@ -2675,23 +2675,23 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B5">
-        <v>4342.404117067667</v>
+        <v>4342.40411706348</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B6">
-        <v>1682.290401537106</v>
+        <v>1682.290401536478</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>1085.076789541974</v>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8">
-        <v>595.9846117540986</v>
+        <v>595.9846117539803</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2710,7 +2710,7 @@
         <v>77</v>
       </c>
       <c r="B9">
-        <v>566.2138795586446</v>
+        <v>566.2138795577548</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2718,15 +2718,15 @@
         <v>41</v>
       </c>
       <c r="B10">
-        <v>558.436708557053</v>
+        <v>558.4367085560835</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B11">
-        <v>480.0729428775501</v>
+        <v>480.0729428774733</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2734,12 +2734,12 @@
         <v>66</v>
       </c>
       <c r="B12">
-        <v>454.6220680693781</v>
+        <v>454.6220680693093</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>447.9616035078638</v>
@@ -2747,23 +2747,23 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>304.3615276910346</v>
+        <v>304.3615276909626</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B15">
-        <v>249.5686071977256</v>
+        <v>249.5686071976911</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>229.3382156558336</v>
@@ -2771,58 +2771,58 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B17">
-        <v>194.2582713928903</v>
+        <v>194.258271392882</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B18">
-        <v>153.3845763081665</v>
+        <v>153.3845763081509</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B19">
-        <v>138.2878417316179</v>
+        <v>138.2878417312995</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B20">
-        <v>130.8879687265438</v>
+        <v>130.887968726462</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B21">
-        <v>83.51115754332133</v>
+        <v>83.51115754331592</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B22">
-        <v>75.68636973166326</v>
+        <v>75.68636973120091</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B23">
-        <v>72.60456492039522</v>
+        <v>72.60456492038352</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2830,63 +2830,63 @@
         <v>73</v>
       </c>
       <c r="B24">
-        <v>51.66726992580963</v>
+        <v>51.66726992578948</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>51.20380519536888</v>
+        <v>51.20380519536801</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B26">
-        <v>46.83760887053438</v>
+        <v>46.8376088705339</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B27">
-        <v>43.03454590898187</v>
+        <v>43.03454590897858</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B28">
-        <v>30.76301699510516</v>
+        <v>30.76301699509802</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B29">
-        <v>27.17469332568114</v>
+        <v>27.17469332567154</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B30">
-        <v>25.61494581798696</v>
+        <v>25.61494581798397</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B31">
-        <v>23.51796923824315</v>
+        <v>23.51796923824291</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2894,7 +2894,7 @@
         <v>64</v>
       </c>
       <c r="B32">
-        <v>21.40264452519152</v>
+        <v>21.40264452519091</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2902,71 +2902,71 @@
         <v>75</v>
       </c>
       <c r="B33">
-        <v>19.95387756392349</v>
+        <v>19.95387756390497</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B34">
-        <v>19.7584177285912</v>
+        <v>19.75841772858955</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35">
-        <v>17.69489186969374</v>
+        <v>17.69489186968478</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B36">
-        <v>16.54251136076972</v>
+        <v>16.54251136074845</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37">
-        <v>15.43429234615746</v>
+        <v>15.43429234615727</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B38">
-        <v>15.39444461608752</v>
+        <v>15.39444461607886</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B39">
-        <v>14.94003159502051</v>
+        <v>14.94003159495474</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>14.57347062388143</v>
+        <v>14.57347062388141</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B41">
-        <v>12.36219577347191</v>
+        <v>12.36219577347118</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2974,31 +2974,31 @@
         <v>62</v>
       </c>
       <c r="B42">
-        <v>11.95349113271388</v>
+        <v>11.95349113270823</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B43">
-        <v>8.395187298679879</v>
+        <v>8.395187298679479</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B44">
-        <v>6.528992849223355</v>
+        <v>6.528992849223204</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B45">
-        <v>5.662198183164302</v>
+        <v>5.662198183163771</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3006,7 +3006,7 @@
         <v>72</v>
       </c>
       <c r="B46">
-        <v>4.020147437396045</v>
+        <v>4.020147437395202</v>
       </c>
     </row>
   </sheetData>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B2">
         <v>753.2485576022657</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>621.1114839490583</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>380.9823484699023</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>240.8006187326834</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>188.1819619401369</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>181.3444851068503</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>128.1428541927552</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>116.4829048019989</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>107.432727539141</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B12">
         <v>105.9383924229766</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>69.89233845381374</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>66.41681104582034</v>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>37.4792836704036</v>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>30.77188782825023</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>29.10006429658621</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>22.79280300677015</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>22.23007628110745</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>14.33108532434674</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B21">
         <v>10.84346846471182</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>10.19234690596405</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B23">
         <v>8.27146775867295</v>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B24">
         <v>5.311883080195145</v>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>422.0086130676058</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>346.3998473209044</v>
@@ -3310,7 +3310,7 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>219.4931181670963</v>
+        <v>219.4931181671017</v>
       </c>
       <c r="C27">
         <v>22</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>189.79501004315</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B29">
         <v>179.4067717773624</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>132.7130497782766</v>
+        <v>132.7130497782785</v>
       </c>
       <c r="C30">
         <v>22</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>128.0659514853349</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>115.9283817184614</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>107.4216866687169</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B34">
-        <v>105.554271212785</v>
+        <v>105.5542712127837</v>
       </c>
       <c r="C34">
         <v>22</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>69.89089256716291</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B36">
         <v>66.38447548042573</v>
@@ -3417,7 +3417,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>37.43626649035554</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <v>27.91863504676936</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>27.28433132420089</v>
+        <v>27.28433132420081</v>
       </c>
       <c r="C39">
         <v>22</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>22.79063724790207</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B41">
         <v>21.59055928657702</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B42">
-        <v>14.30329344853825</v>
+        <v>14.30329344853827</v>
       </c>
       <c r="C42">
         <v>22</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B43">
         <v>10.6718878546015</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>10.0604212294024</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B45">
         <v>8.181182066549855</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B46">
         <v>5.293406540666596</v>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B47">
         <v>357.4257975790996</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B48">
         <v>189.7942844355019</v>
@@ -3552,7 +3552,7 @@
         <v>41</v>
       </c>
       <c r="B49">
-        <v>188.9902426317829</v>
+        <v>188.990242631779</v>
       </c>
       <c r="C49">
         <v>21</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>179.1814069875248</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B51">
         <v>132.0222523218312</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>126.1586516393311</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>104.9230735305154</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B54">
         <v>104.2045795027387</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B55">
         <v>63.41801463944181</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B56">
         <v>52.46578351689658</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B57">
         <v>45.495271078065</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B58">
         <v>36.10119196016667</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B59">
-        <v>27.75878518411511</v>
+        <v>27.75878518411502</v>
       </c>
       <c r="C59">
         <v>21</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B60">
-        <v>27.15714572046759</v>
+        <v>27.15714572046898</v>
       </c>
       <c r="C60">
         <v>21</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B61">
         <v>21.91736931385755</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B62">
         <v>21.52430363558362</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B63">
         <v>14.30321890244352</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B64">
         <v>10.37576715802304</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B65">
-        <v>9.997659611193187</v>
+        <v>9.997659611193177</v>
       </c>
       <c r="C65">
         <v>21</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B66">
         <v>7.725803353467899</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B67">
-        <v>4.891716487339313</v>
+        <v>4.891716487339307</v>
       </c>
       <c r="C67">
         <v>21</v>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B68">
         <v>350.15876700362</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B70">
         <v>131.0438925187317</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B71">
         <v>126.1229198142555</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B72">
         <v>104.8554203896614</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B73">
         <v>104.3542372875243</v>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B74">
         <v>104.0995837087193</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B75">
         <v>62.98166131595279</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B76">
         <v>51.41561844665483</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B77">
         <v>44.37256131248959</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B78">
         <v>36.08640639475832</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B79">
-        <v>25.961573069803</v>
+        <v>25.96157306980502</v>
       </c>
       <c r="C79">
         <v>20</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B80">
         <v>23.17873712735706</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B81">
         <v>21.82413329779819</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B82">
         <v>20.79939098743634</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B83">
         <v>14.26568970528629</v>
@@ -3934,10 +3934,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B84">
-        <v>10.23638198844316</v>
+        <v>10.23638198844317</v>
       </c>
       <c r="C84">
         <v>20</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B85">
-        <v>9.91507444666936</v>
+        <v>9.915074446669371</v>
       </c>
       <c r="C85">
         <v>20</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B86">
         <v>7.32403401602895</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B87">
         <v>4.831489521602753</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B88">
         <v>343.2179446958474</v>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B89">
         <v>125.5077947003103</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B90">
         <v>104.825392379835</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B91">
         <v>102.7342881718347</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B92">
         <v>99.08996399137929</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B93">
         <v>62.8237503697218</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B94">
         <v>46.95493907675103</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B95">
         <v>39.51026475811477</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B96">
-        <v>39.0956263428038</v>
+        <v>39.0956263428043</v>
       </c>
       <c r="C96">
         <v>19</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B97">
         <v>36.04227281002906</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B98">
-        <v>24.14425539597872</v>
+        <v>24.14425539597859</v>
       </c>
       <c r="C98">
         <v>19</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B99">
         <v>22.98444763052662</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B100">
         <v>21.81186898247412</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B101">
         <v>20.75482064928144</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B102">
         <v>14.25964084319195</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B103">
         <v>10.17773142116928</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B104">
-        <v>9.675462750088021</v>
+        <v>9.675462750088085</v>
       </c>
       <c r="C104">
         <v>19</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B105">
         <v>6.971737396184158</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B106">
-        <v>4.817591621498238</v>
+        <v>4.817591621498235</v>
       </c>
       <c r="C106">
         <v>19</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B107">
         <v>325.8334767589092</v>
@@ -4198,7 +4198,7 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B108">
         <v>103.2454978961491</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B109">
         <v>89.07234938360985</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B110">
         <v>61.19465090839606</v>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B111">
         <v>49.39608223071544</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B112">
         <v>46.38481381734387</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B113">
-        <v>38.92800648120037</v>
+        <v>38.92800648120138</v>
       </c>
       <c r="C113">
         <v>18</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B114">
         <v>38.88411173586185</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B115">
         <v>35.88521271312028</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B116">
-        <v>23.18050670244269</v>
+        <v>23.18050670244102</v>
       </c>
       <c r="C116">
         <v>18</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B117">
         <v>22.92479218183164</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B118">
-        <v>21.51003779407004</v>
+        <v>21.51003779406999</v>
       </c>
       <c r="C118">
         <v>18</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B119">
         <v>20.7524511151648</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B120">
         <v>12.79881898025029</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B121">
         <v>9.880319222305943</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B122">
-        <v>9.600800686534079</v>
+        <v>9.60080068653409</v>
       </c>
       <c r="C122">
         <v>18</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B123">
         <v>6.97106031234692</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B124">
         <v>4.687496588907403</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B125">
         <v>322.6389566022954</v>
@@ -4396,10 +4396,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B126">
-        <v>88.99783104935099</v>
+        <v>88.99783104935011</v>
       </c>
       <c r="C126">
         <v>17</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B127">
         <v>48.1790112167141</v>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B128">
         <v>45.70723006156884</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B129">
         <v>45.08386262786938</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B130">
         <v>38.85422979982847</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B131">
-        <v>38.84650196528849</v>
+        <v>38.84650196528916</v>
       </c>
       <c r="C131">
         <v>17</v>
@@ -4462,10 +4462,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B132">
-        <v>23.0109921871439</v>
+        <v>23.01099218714343</v>
       </c>
       <c r="C132">
         <v>17</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B133">
         <v>22.3798010065938</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B134">
         <v>20.3497706928474</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B135">
         <v>16.31257720737751</v>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B136">
         <v>11.82500525076815</v>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B137">
-        <v>9.714837338564072</v>
+        <v>9.714837338564061</v>
       </c>
       <c r="C137">
         <v>17</v>
@@ -4528,10 +4528,10 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B138">
-        <v>9.596838586938988</v>
+        <v>9.59683858693902</v>
       </c>
       <c r="C138">
         <v>17</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B139">
         <v>8.399152362778796</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B140">
         <v>6.967033596079141</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B141">
-        <v>4.496132212181966</v>
+        <v>4.496132212181964</v>
       </c>
       <c r="C141">
         <v>17</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B142">
         <v>140.1478292398132</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B143">
         <v>44.84253904500241</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B144">
         <v>43.50095480776146</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B145">
         <v>40.29112695258199</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B146">
         <v>38.6006720586165</v>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B147">
-        <v>35.12467116551955</v>
+        <v>35.12467116551969</v>
       </c>
       <c r="C147">
         <v>16</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B148">
         <v>22.16735339425238</v>
@@ -4649,10 +4649,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B149">
-        <v>20.28931570756037</v>
+        <v>20.28931570756229</v>
       </c>
       <c r="C149">
         <v>16</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B150">
         <v>19.79668146121563</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B151">
         <v>16.30674433410469</v>
@@ -4682,7 +4682,7 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B152">
         <v>11.76593855010928</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B153">
         <v>9.348473645893128</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B154">
-        <v>8.548515166014315</v>
+        <v>8.548515166014372</v>
       </c>
       <c r="C154">
         <v>16</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B155">
         <v>8.382170556852792</v>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B156">
         <v>6.961559168749637</v>
@@ -4737,10 +4737,10 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B157">
-        <v>4.334299968408972</v>
+        <v>4.33429996840897</v>
       </c>
       <c r="C157">
         <v>16</v>
@@ -4748,7 +4748,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B158">
         <v>129.436329519668</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B159">
         <v>40.68773326028861</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B160">
         <v>38.38608295896825</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B161">
         <v>37.78216414725723</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B162">
-        <v>35.11422483991199</v>
+        <v>35.11422483991172</v>
       </c>
       <c r="C162">
         <v>15</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B163">
         <v>22.06799815402378</v>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B164">
-        <v>20.25288361463828</v>
+        <v>20.25288361463705</v>
       </c>
       <c r="C164">
         <v>15</v>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B165">
         <v>19.5586704774933</v>
@@ -4836,10 +4836,10 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B166">
-        <v>11.59355630704117</v>
+        <v>11.59355630704115</v>
       </c>
       <c r="C166">
         <v>15</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B167">
         <v>9.278024967226109</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B168">
-        <v>8.36067338959918</v>
+        <v>8.360673389599295</v>
       </c>
       <c r="C168">
         <v>15</v>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B169">
-        <v>8.320184649648382</v>
+        <v>8.320184649648375</v>
       </c>
       <c r="C169">
         <v>15</v>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B170">
-        <v>6.960425926140311</v>
+        <v>6.960425926140306</v>
       </c>
       <c r="C170">
         <v>15</v>
@@ -4891,10 +4891,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B171">
-        <v>4.30827516475888</v>
+        <v>4.308275164758875</v>
       </c>
       <c r="C171">
         <v>15</v>
@@ -4902,10 +4902,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B172">
-        <v>3.496694847179452</v>
+        <v>3.496694847179453</v>
       </c>
       <c r="C172">
         <v>15</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B173">
         <v>38.30554975157519</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B174">
         <v>36.818409209265</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B175">
         <v>34.36782976970145</v>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B176">
         <v>33.41256846109296</v>
@@ -4957,7 +4957,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B177">
         <v>20.93493421373343</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B178">
         <v>19.67072465141573</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B179">
         <v>19.55064341645915</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B180">
         <v>11.59349759414457</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B181">
         <v>9.152024358088712</v>
@@ -5012,10 +5012,10 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B182">
-        <v>8.285392754354749</v>
+        <v>8.285392754354742</v>
       </c>
       <c r="C182">
         <v>14</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B183">
         <v>8.236562852304273</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B184">
-        <v>4.869695992243043</v>
+        <v>4.86969599224304</v>
       </c>
       <c r="C184">
         <v>14</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B185">
         <v>4.299895480700423</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B186">
-        <v>3.460355648131094</v>
+        <v>3.460355648131096</v>
       </c>
       <c r="C186">
         <v>14</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B187">
         <v>33.76069752475988</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B188">
         <v>18.46734346847535</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B189">
         <v>17.6210434341042</v>
@@ -5100,7 +5100,7 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B190">
         <v>17.59158649310429</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B191">
-        <v>15.64017833635287</v>
+        <v>15.64017833635289</v>
       </c>
       <c r="C191">
         <v>13</v>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B192">
         <v>15.36259547621222</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B193">
         <v>11.31393158214105</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B194">
         <v>9.134150411590875</v>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B195">
         <v>8.275924596400808</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B196">
         <v>8.222138054169125</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B197">
-        <v>4.299879571629114</v>
+        <v>4.299879571629109</v>
       </c>
       <c r="C197">
         <v>13</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B198">
-        <v>4.288901189139287</v>
+        <v>4.288901189139285</v>
       </c>
       <c r="C198">
         <v>13</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B199">
-        <v>3.459360250067372</v>
+        <v>3.459360250067371</v>
       </c>
       <c r="C199">
         <v>13</v>
@@ -5210,10 +5210,10 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B200">
-        <v>18.17565181127735</v>
+        <v>18.17565181127732</v>
       </c>
       <c r="C200">
         <v>12</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B201">
-        <v>17.40673623527652</v>
+        <v>17.40673623527648</v>
       </c>
       <c r="C201">
         <v>12</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B202">
         <v>17.13118197775876</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B203">
         <v>14.39853703421182</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B204">
         <v>13.48967477870826</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B205">
         <v>9.196729797502988</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B206">
         <v>8.1377404024605</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B207">
         <v>8.106177683033685</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B208">
         <v>7.983058193099758</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B209">
         <v>4.284913595581624</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B210">
-        <v>4.155321222230115</v>
+        <v>4.155321222230113</v>
       </c>
       <c r="C210">
         <v>12</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B211">
-        <v>2.921413940709788</v>
+        <v>2.921413940709789</v>
       </c>
       <c r="C211">
         <v>12</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B212">
         <v>15.31961240769551</v>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B213">
         <v>13.87521511487681</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B214">
         <v>13.45901133265104</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B215">
         <v>8.983731020786701</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B216">
-        <v>8.553962594638444</v>
+        <v>8.553962594638225</v>
       </c>
       <c r="C216">
         <v>11</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B217">
-        <v>8.091616687276078</v>
+        <v>8.091616687272305</v>
       </c>
       <c r="C217">
         <v>11</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B218">
         <v>7.8898703803859</v>
@@ -5419,7 +5419,7 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B219">
         <v>7.524606276423378</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B220">
         <v>4.100611879847337</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B221">
         <v>4.036473394325227</v>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B222">
         <v>2.895520501329768</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B223">
         <v>12.05912487566963</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B224">
         <v>11.69732704581562</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B225">
         <v>8.956269493730833</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B226">
-        <v>8.46997505761181</v>
+        <v>8.469975057611229</v>
       </c>
       <c r="C226">
         <v>10</v>
@@ -5507,10 +5507,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B227">
-        <v>7.764705303209216</v>
+        <v>7.764705303210575</v>
       </c>
       <c r="C227">
         <v>10</v>
@@ -5518,10 +5518,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B228">
-        <v>7.258695407782738</v>
+        <v>7.258695407782731</v>
       </c>
       <c r="C228">
         <v>10</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B229">
         <v>6.183862547209465</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B230">
         <v>3.928122511751938</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B231">
         <v>3.639712619918944</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B232">
         <v>2.893097787189105</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B233">
         <v>11.47430877943272</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B234">
         <v>7.540077819986799</v>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B235">
         <v>6.758127586816794</v>
@@ -5606,10 +5606,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B236">
-        <v>5.611296802160668</v>
+        <v>5.611296802159213</v>
       </c>
       <c r="C236">
         <v>9</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B237">
         <v>5.536584629465203</v>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B238">
-        <v>4.269237442242018</v>
+        <v>4.269237442241603</v>
       </c>
       <c r="C238">
         <v>9</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B239">
         <v>3.635663641156808</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B240">
         <v>3.203374240829735</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B241">
-        <v>2.886364388706139</v>
+        <v>2.88636438870614</v>
       </c>
       <c r="C241">
         <v>9</v>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B2">
         <v>11.47430877943272</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>7.540077819986799</v>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>6.758127586816794</v>
@@ -5714,15 +5714,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>5.611296802160668</v>
+        <v>5.611296802159213</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>5.536584629465203</v>
@@ -5730,15 +5730,15 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B7">
-        <v>4.269237442242018</v>
+        <v>4.269237442241603</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B8">
         <v>3.635663641156808</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>3.203374240829735</v>
@@ -5754,10 +5754,10 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B10">
-        <v>2.886364388706139</v>
+        <v>2.88636438870614</v>
       </c>
     </row>
   </sheetData>
@@ -5777,47 +5777,47 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
